--- a/X-Raya-roles.xlsx
+++ b/X-Raya-roles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I92"/>
+  <dimension ref="A1:I130"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -644,7 +644,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>TeamLead</v>
+        <v>ITManager</v>
       </c>
       <c r="B9" t="str">
         <v>it</v>
@@ -656,24 +656,24 @@
         <v/>
       </c>
       <c r="E9" t="str">
-        <v>lead</v>
+        <v>engineering manager</v>
       </c>
       <c r="F9" t="str">
-        <v>тимлид</v>
+        <v>руководитель ит</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Team Lead | Tech Lead | Lead Developer | Engineering Manager | тимлид | техлид</v>
+        <v>IT Group Manager | IT Manager | руководитель IT-отдела</v>
       </c>
       <c r="I9" t="str">
-        <v>team lead | teamlead | тимлид | tech lead | техлид | тех лид | lead developer | engineering manager | руководитель группы разработки</v>
+        <v>it group manager | it manager | руководитель ит | ит менеджер | руководитель ит отдела | начальник ит</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>DeliveryManager</v>
+        <v>TeamLead</v>
       </c>
       <c r="B10" t="str">
         <v>it</v>
@@ -685,24 +685,24 @@
         <v/>
       </c>
       <c r="E10" t="str">
-        <v>delivery</v>
+        <v>lead</v>
       </c>
       <c r="F10" t="str">
-        <v>delivery-менеджер</v>
+        <v>тимлид</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Delivery Manager | Program Manager | руководитель поставки</v>
+        <v>Team Lead | Tech Lead | Lead Developer | Engineering Manager | тимлид | техлид</v>
       </c>
       <c r="I10" t="str">
-        <v>delivery manager | деливери менеджер | program manager | программный менеджер | руководитель программ</v>
+        <v>team lead | teamlead | тимлид | tech lead | техлид | тех лид | lead developer | engineering manager | руководитель группы разработки</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>HeadOfQA</v>
+        <v>DeliveryManager</v>
       </c>
       <c r="B11" t="str">
         <v>it</v>
@@ -714,24 +714,24 @@
         <v/>
       </c>
       <c r="E11" t="str">
-        <v>qa</v>
+        <v>delivery</v>
       </c>
       <c r="F11" t="str">
-        <v>руководитель тестирования</v>
+        <v>delivery-менеджер</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Head of QA | QA Lead | руководитель отдела тестирования</v>
+        <v>Delivery Manager | Program Manager | руководитель поставки</v>
       </c>
       <c r="I11" t="str">
-        <v>head of qa | qa lead | руководитель тестирования | руководитель отдела тестирования | qa manager</v>
+        <v>delivery manager | деливери менеджер | program manager | программный менеджер | руководитель программ</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>HeadOfData</v>
+        <v>HeadOfQA</v>
       </c>
       <c r="B12" t="str">
         <v>it</v>
@@ -740,27 +740,27 @@
         <v>exec</v>
       </c>
       <c r="D12" t="str">
-        <v>kaggle | hf</v>
+        <v/>
       </c>
       <c r="E12" t="str">
-        <v>data</v>
+        <v>qa</v>
       </c>
       <c r="F12" t="str">
-        <v>руководитель data</v>
+        <v>руководитель тестирования</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Head of Data | Head of Analytics | руководитель аналитики</v>
+        <v>Head of QA | QA Lead | руководитель отдела тестирования</v>
       </c>
       <c r="I12" t="str">
-        <v>head of data | head of analytics | руководитель аналитики | руководитель отдела данных | lead data scientist</v>
+        <v>head of qa | qa lead | руководитель тестирования | руководитель отдела тестирования | qa manager</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>HeadOfDesign</v>
+        <v>HeadOfData</v>
       </c>
       <c r="B13" t="str">
         <v>it</v>
@@ -769,56 +769,56 @@
         <v>exec</v>
       </c>
       <c r="D13" t="str">
-        <v>behance | dribbble</v>
+        <v>kaggle | hf</v>
       </c>
       <c r="E13" t="str">
-        <v/>
+        <v>data</v>
       </c>
       <c r="F13" t="str">
-        <v>арт-директор</v>
+        <v>руководитель data</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Head of Design | Design Lead | Art Director | арт-директор</v>
+        <v>Head of Data | Head of Analytics | руководитель аналитики</v>
       </c>
       <c r="I13" t="str">
-        <v>head of design | design lead | арт директор | art director | design director | руководитель дизайна</v>
+        <v>head of data | head of analytics | руководитель аналитики | руководитель отдела данных | lead data scientist</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Frontend</v>
+        <v>HeadOfDesign</v>
       </c>
       <c r="B14" t="str">
         <v>it</v>
       </c>
       <c r="C14" t="str">
-        <v/>
+        <v>exec</v>
       </c>
       <c r="D14" t="str">
-        <v/>
+        <v>behance | dribbble</v>
       </c>
       <c r="E14" t="str">
-        <v>frontend developer</v>
+        <v/>
       </c>
       <c r="F14" t="str">
-        <v>фронтенд разработчик</v>
+        <v>арт-директор</v>
       </c>
       <c r="G14" t="str">
-        <v>JavaScript | React</v>
+        <v/>
       </c>
       <c r="H14" t="str">
-        <v>Frontend Developer | Front-end Developer | Frontend Engineer | фронтенд разработчик | фронтендер</v>
+        <v>Head of Design | Design Lead | Art Director | арт-директор</v>
       </c>
       <c r="I14" t="str">
-        <v>frontend | front end | фронтенд | фронтендер | фронтенд разработчик | ui developer | верстальщик</v>
+        <v>head of design | design lead | арт директор | art director | design director | руководитель дизайна</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Backend</v>
+        <v>Frontend</v>
       </c>
       <c r="B15" t="str">
         <v>it</v>
@@ -830,24 +830,24 @@
         <v/>
       </c>
       <c r="E15" t="str">
-        <v>backend developer</v>
+        <v>frontend developer</v>
       </c>
       <c r="F15" t="str">
-        <v>бэкенд разработчик</v>
+        <v>фронтенд разработчик</v>
       </c>
       <c r="G15" t="str">
-        <v/>
+        <v>JavaScript | React</v>
       </c>
       <c r="H15" t="str">
-        <v>Backend Developer | Back-end Developer | Backend Engineer | бэкенд разработчик | серверный разработчик</v>
+        <v>Frontend Developer | Front-end Developer | Frontend Engineer | фронтенд разработчик | фронтендер</v>
       </c>
       <c r="I15" t="str">
-        <v>backend | back end | бэкенд | бекенд | бэкендер | бэкенд разработчик | серверный разработчик | серверная разработка</v>
+        <v>frontend | front end | фронтенд | фронтендер | фронтенд разработчик | ui developer | верстальщик</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Fullstack</v>
+        <v>Backend</v>
       </c>
       <c r="B16" t="str">
         <v>it</v>
@@ -859,24 +859,24 @@
         <v/>
       </c>
       <c r="E16" t="str">
-        <v>fullstack developer</v>
+        <v>backend developer</v>
       </c>
       <c r="F16" t="str">
-        <v>фулстек разработчик</v>
+        <v>бэкенд разработчик</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Fullstack Developer | Full stack Developer | фулстек разработчик</v>
+        <v>Backend Developer | Back-end Developer | Backend Engineer | бэкенд разработчик | серверный разработчик</v>
       </c>
       <c r="I16" t="str">
-        <v>fullstack | full stack | фулстек | фуллстек | фулстек разработчик | фуллстек разработчик</v>
+        <v>backend | back end | бэкенд | бекенд | бэкендер | бэкенд разработчик | серверный разработчик | серверная разработка | node.js | node js |  node  | нода</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Mobile</v>
+        <v>Fullstack</v>
       </c>
       <c r="B17" t="str">
         <v>it</v>
@@ -888,24 +888,24 @@
         <v/>
       </c>
       <c r="E17" t="str">
-        <v>mobile developer</v>
+        <v>fullstack developer</v>
       </c>
       <c r="F17" t="str">
-        <v>мобильный разработчик</v>
+        <v>фулстек разработчик</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Mobile Developer | мобильный разработчик</v>
+        <v>Fullstack Developer | Full stack Developer | фулстек разработчик</v>
       </c>
       <c r="I17" t="str">
-        <v>mobile developer | мобильный разработчик | мобильная разработка</v>
+        <v>fullstack | full stack | фулстек | фуллстек | фулстек разработчик | фуллстек разработчик</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Android</v>
+        <v>Mobile</v>
       </c>
       <c r="B18" t="str">
         <v>it</v>
@@ -917,24 +917,24 @@
         <v/>
       </c>
       <c r="E18" t="str">
-        <v>android</v>
+        <v>mobile developer</v>
       </c>
       <c r="F18" t="str">
-        <v>android разработчик</v>
+        <v>мобильный разработчик</v>
       </c>
       <c r="G18" t="str">
-        <v>Kotlin</v>
+        <v/>
       </c>
       <c r="H18" t="str">
-        <v>Android Developer | Kotlin Developer | андроид разработчик</v>
+        <v>Mobile Developer | мобильный разработчик</v>
       </c>
       <c r="I18" t="str">
-        <v>android developer | android разработчик | андроид разработчик | android | андроид</v>
+        <v>mobile developer | мобильный разработчик | мобильная разработка</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>iOS</v>
+        <v>Android</v>
       </c>
       <c r="B19" t="str">
         <v>it</v>
@@ -946,24 +946,24 @@
         <v/>
       </c>
       <c r="E19" t="str">
-        <v>ios</v>
+        <v>android</v>
       </c>
       <c r="F19" t="str">
-        <v>ios разработчик</v>
+        <v>android разработчик</v>
       </c>
       <c r="G19" t="str">
-        <v>Swift</v>
+        <v>Kotlin</v>
       </c>
       <c r="H19" t="str">
-        <v>iOS Developer | Swift Developer | ios разработчик</v>
+        <v>Android Developer | Kotlin Developer | андроид разработчик</v>
       </c>
       <c r="I19" t="str">
-        <v xml:space="preserve"> ios  | ios developer | ios разработчик | разработчик ios | swift developer</v>
+        <v>android developer | android разработчик | андроид разработчик | android | андроид</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Flutter</v>
+        <v>iOS</v>
       </c>
       <c r="B20" t="str">
         <v>it</v>
@@ -975,24 +975,24 @@
         <v/>
       </c>
       <c r="E20" t="str">
-        <v>flutter</v>
+        <v>ios</v>
       </c>
       <c r="F20" t="str">
-        <v>flutter разработчик</v>
+        <v>ios разработчик</v>
       </c>
       <c r="G20" t="str">
-        <v/>
+        <v>Swift</v>
       </c>
       <c r="H20" t="str">
-        <v>Flutter Developer | Dart Developer | flutter разработчик</v>
+        <v>iOS Developer | Swift Developer | ios разработчик</v>
       </c>
       <c r="I20" t="str">
-        <v>flutter developer | flutter разработчик | флаттер | flutter</v>
+        <v xml:space="preserve"> ios  | ios developer | ios разработчик | разработчик ios | swift developer</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ReactNative</v>
+        <v>Flutter</v>
       </c>
       <c r="B21" t="str">
         <v>it</v>
@@ -1004,24 +1004,24 @@
         <v/>
       </c>
       <c r="E21" t="str">
-        <v>react-native</v>
+        <v>flutter</v>
       </c>
       <c r="F21" t="str">
-        <v>react native разработчик</v>
+        <v>flutter разработчик</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>React Native Developer | react native разработчик</v>
+        <v>Flutter Developer | Dart Developer | flutter разработчик</v>
       </c>
       <c r="I21" t="str">
-        <v>react native | реакт натив | react native developer</v>
+        <v>flutter developer | flutter разработчик | флаттер | flutter</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Desktop</v>
+        <v>ReactNative</v>
       </c>
       <c r="B22" t="str">
         <v>it</v>
@@ -1033,24 +1033,24 @@
         <v/>
       </c>
       <c r="E22" t="str">
-        <v>desktop</v>
+        <v>react-native</v>
       </c>
       <c r="F22" t="str">
-        <v>desktop разработчик</v>
+        <v>react native разработчик</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Desktop Developer | C++ Developer | десктоп разработчик</v>
+        <v>React Native Developer | react native разработчик</v>
       </c>
       <c r="I22" t="str">
-        <v>desktop developer | десктоп разработчик | разработчик десктопных приложений</v>
+        <v>react native | реакт натив | react native developer</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>GameDev</v>
+        <v>Desktop</v>
       </c>
       <c r="B23" t="str">
         <v>it</v>
@@ -1062,24 +1062,24 @@
         <v/>
       </c>
       <c r="E23" t="str">
-        <v>game developer</v>
+        <v>desktop</v>
       </c>
       <c r="F23" t="str">
-        <v>разработчик игр</v>
+        <v>desktop разработчик</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Game Developer | Gameplay Programmer | разработчик игр</v>
+        <v>Desktop Developer | C++ Developer | десктоп разработчик</v>
       </c>
       <c r="I23" t="str">
-        <v>game developer | геймдев | разработчик игр | гейм разработчик</v>
+        <v>desktop developer | десктоп разработчик | разработчик десктопных приложений</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Unity</v>
+        <v>GameDev</v>
       </c>
       <c r="B24" t="str">
         <v>it</v>
@@ -1091,24 +1091,24 @@
         <v/>
       </c>
       <c r="E24" t="str">
-        <v>unity</v>
+        <v>game developer</v>
       </c>
       <c r="F24" t="str">
-        <v>unity разработчик</v>
+        <v>разработчик игр</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Unity Developer | unity разработчик</v>
+        <v>Game Developer | Gameplay Programmer | разработчик игр</v>
       </c>
       <c r="I24" t="str">
-        <v>unity developer | unity разработчик | юнити</v>
+        <v>game developer | геймдев | разработчик игр | гейм разработчик</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Unreal</v>
+        <v>Unity</v>
       </c>
       <c r="B25" t="str">
         <v>it</v>
@@ -1120,24 +1120,24 @@
         <v/>
       </c>
       <c r="E25" t="str">
-        <v>unreal</v>
+        <v>unity</v>
       </c>
       <c r="F25" t="str">
-        <v>unreal разработчик</v>
+        <v>unity разработчик</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Unreal Engine Developer | C++ Game Developer</v>
+        <v>Unity Developer | unity разработчик</v>
       </c>
       <c r="I25" t="str">
-        <v>unreal developer | unreal engine | анрил</v>
+        <v>unity developer | unity разработчик | юнити</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Embedded</v>
+        <v>Unreal</v>
       </c>
       <c r="B26" t="str">
         <v>it</v>
@@ -1149,24 +1149,24 @@
         <v/>
       </c>
       <c r="E26" t="str">
-        <v>embedded</v>
+        <v>unreal</v>
       </c>
       <c r="F26" t="str">
-        <v>разработчик встраиваемых систем</v>
+        <v>unreal разработчик</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Embedded Developer | Firmware Engineer | разработчик встраиваемых систем</v>
+        <v>Unreal Engine Developer | C++ Game Developer</v>
       </c>
       <c r="I26" t="str">
-        <v>embedded | встраиваемые системы | прошивки | микроконтроллеры | firmware | эмбеддед</v>
+        <v>unreal developer | unreal engine | анрил</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Blockchain</v>
+        <v>Embedded</v>
       </c>
       <c r="B27" t="str">
         <v>it</v>
@@ -1178,24 +1178,24 @@
         <v/>
       </c>
       <c r="E27" t="str">
-        <v>blockchain</v>
+        <v>embedded</v>
       </c>
       <c r="F27" t="str">
-        <v>блокчейн разработчик</v>
+        <v>разработчик встраиваемых систем</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Blockchain Developer | Smart Contract Developer | Solidity Developer | web3 разработчик</v>
+        <v>Embedded Developer | Firmware Engineer | разработчик встраиваемых систем</v>
       </c>
       <c r="I27" t="str">
-        <v>blockchain developer | блокчейн разработчик | smart contract | solidity | web3 | веб3</v>
+        <v>embedded | встраиваемые системы | прошивки | микроконтроллеры | firmware | эмбеддед</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>OneC</v>
+        <v>Blockchain</v>
       </c>
       <c r="B28" t="str">
         <v>it</v>
@@ -1207,24 +1207,24 @@
         <v/>
       </c>
       <c r="E28" t="str">
-        <v>1c developer</v>
+        <v>blockchain</v>
       </c>
       <c r="F28" t="str">
-        <v>1с разработчик</v>
+        <v>блокчейн разработчик</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>1С-разработчик | 1C Developer | Программист 1С</v>
+        <v>Blockchain Developer | Smart Contract Developer | Solidity Developer | web3 разработчик</v>
       </c>
       <c r="I28" t="str">
-        <v>1с разработчик | 1c developer | программист 1с | разработчик 1с | 1с программист</v>
+        <v>blockchain developer | блокчейн разработчик | smart contract | solidity | web3 | веб3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Bitrix</v>
+        <v>OneC</v>
       </c>
       <c r="B29" t="str">
         <v>it</v>
@@ -1236,24 +1236,24 @@
         <v/>
       </c>
       <c r="E29" t="str">
-        <v>bitrix developer</v>
+        <v>1c developer</v>
       </c>
       <c r="F29" t="str">
-        <v>битрикс разработчик</v>
+        <v>1с разработчик</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Bitrix-разработчик | 1C-Bitrix Developer | разработчик Битрикс</v>
+        <v>1С-разработчик | 1C Developer | Программист 1С | 1С аналитик</v>
       </c>
       <c r="I29" t="str">
-        <v>битрикс разработчик | bitrix developer | разработчик битрикс | 1с битрикс</v>
+        <v xml:space="preserve">1с разработчик | 1c developer | программист 1с | разработчик 1с | 1с программист | 1c аналитик | 1с аналитик |  1c  |  1с </v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>WordPress</v>
+        <v>Bitrix</v>
       </c>
       <c r="B30" t="str">
         <v>it</v>
@@ -1265,24 +1265,24 @@
         <v/>
       </c>
       <c r="E30" t="str">
-        <v>wordpress</v>
+        <v>bitrix developer</v>
       </c>
       <c r="F30" t="str">
-        <v>wordpress разработчик</v>
+        <v>битрикс разработчик</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>WordPress Developer | CMS Developer</v>
+        <v>Bitrix-разработчик | 1C-Bitrix Developer | разработчик Битрикс</v>
       </c>
       <c r="I30" t="str">
-        <v>wordpress developer | вордпресс | разработчик wordpress | cms разработчик</v>
+        <v>битрикс разработчик | bitrix developer | разработчик битрикс | 1с битрикс</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Developer</v>
+        <v>WordPress</v>
       </c>
       <c r="B31" t="str">
         <v>it</v>
@@ -1294,24 +1294,24 @@
         <v/>
       </c>
       <c r="E31" t="str">
-        <v>developer</v>
+        <v>wordpress</v>
       </c>
       <c r="F31" t="str">
-        <v>разработчик</v>
+        <v>wordpress разработчик</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Developer | Software Engineer | разработчик | программист | инженер-программист</v>
+        <v>WordPress Developer | CMS Developer</v>
       </c>
       <c r="I31" t="str">
-        <v>разработчик | программист | software engineer | software developer | developer |  dev  | кодер | инженер программист</v>
+        <v>wordpress developer | вордпресс | разработчик wordpress | cms разработчик</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>DataScientist</v>
+        <v>Developer</v>
       </c>
       <c r="B32" t="str">
         <v>it</v>
@@ -1320,27 +1320,27 @@
         <v/>
       </c>
       <c r="D32" t="str">
-        <v>kaggle | hf</v>
+        <v/>
       </c>
       <c r="E32" t="str">
-        <v>data scientist</v>
+        <v>developer</v>
       </c>
       <c r="F32" t="str">
-        <v>дата-сайентист</v>
+        <v>разработчик</v>
       </c>
       <c r="G32" t="str">
-        <v>Python</v>
+        <v/>
       </c>
       <c r="H32" t="str">
-        <v>Data Scientist | дата-сайентист | специалист по data science</v>
+        <v>Developer | Software Engineer | разработчик | программист | инженер-программист</v>
       </c>
       <c r="I32" t="str">
-        <v>data scientist | дата сайентист | датасайнтист | data science | дата саенс</v>
+        <v>разработчик | программист | software engineer | software developer | developer |  dev  | кодер | инженер программист | staff engineer | стафф инженер | core engineering | инженерные должности</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>DataEngineer</v>
+        <v>DataScientist</v>
       </c>
       <c r="B33" t="str">
         <v>it</v>
@@ -1349,27 +1349,27 @@
         <v/>
       </c>
       <c r="D33" t="str">
-        <v>kaggle</v>
+        <v>kaggle | hf</v>
       </c>
       <c r="E33" t="str">
-        <v>data engineer</v>
+        <v>data scientist</v>
       </c>
       <c r="F33" t="str">
-        <v>дата-инженер</v>
+        <v>дата-сайентист</v>
       </c>
       <c r="G33" t="str">
-        <v>Python | SQL | Spark</v>
+        <v>Python</v>
       </c>
       <c r="H33" t="str">
-        <v>Data Engineer | дата-инженер | инженер данных</v>
+        <v>Data Scientist | дата-сайентист | специалист по data science</v>
       </c>
       <c r="I33" t="str">
-        <v>data engineer | дата инженер | инженер данных | дата инжиниринг</v>
+        <v>data scientist | дата сайентист | датасайнтист | data science | дата саенс</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>MLEngineer</v>
+        <v>DataEngineer</v>
       </c>
       <c r="B34" t="str">
         <v>it</v>
@@ -1378,27 +1378,27 @@
         <v/>
       </c>
       <c r="D34" t="str">
-        <v>kaggle | hf</v>
+        <v>kaggle</v>
       </c>
       <c r="E34" t="str">
-        <v>machine learning</v>
+        <v>data engineer</v>
       </c>
       <c r="F34" t="str">
-        <v>ml-инженер</v>
+        <v>дата-инженер</v>
       </c>
       <c r="G34" t="str">
-        <v>Python</v>
+        <v>Python | SQL | Spark</v>
       </c>
       <c r="H34" t="str">
-        <v>ML Engineer | Machine Learning Engineer | ml-инженер</v>
+        <v>Data Engineer | дата-инженер | инженер данных</v>
       </c>
       <c r="I34" t="str">
-        <v>ml engineer | мл инженер | machine learning engineer | инженер машинного обучения | ml</v>
+        <v>data engineer | дата инженер | инженер данных | дата инжиниринг | platform data engineer</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>MLOps</v>
+        <v>MLEngineer</v>
       </c>
       <c r="B35" t="str">
         <v>it</v>
@@ -1407,27 +1407,27 @@
         <v/>
       </c>
       <c r="D35" t="str">
-        <v>hf</v>
+        <v>kaggle | hf</v>
       </c>
       <c r="E35" t="str">
-        <v>mlops</v>
+        <v>machine learning</v>
       </c>
       <c r="F35" t="str">
-        <v>mlops-инженер</v>
+        <v>ml-инженер</v>
       </c>
       <c r="G35" t="str">
-        <v>Docker | Kubernetes | Python</v>
+        <v>Python</v>
       </c>
       <c r="H35" t="str">
-        <v>MLOps Engineer | ML Platform Engineer | mlops-инженер</v>
+        <v>ML Engineer | Machine Learning Engineer | ml-инженер</v>
       </c>
       <c r="I35" t="str">
-        <v>mlops | ml ops | mlops engineer | ml платформа</v>
+        <v>ml engineer | мл инженер | machine learning engineer | machine learning | инженер машинного обучения | машинное обучение | ml</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>DataAnalyst</v>
+        <v>MLOps</v>
       </c>
       <c r="B36" t="str">
         <v>it</v>
@@ -1436,27 +1436,27 @@
         <v/>
       </c>
       <c r="D36" t="str">
-        <v>kaggle</v>
+        <v>hf</v>
       </c>
       <c r="E36" t="str">
-        <v>data analyst</v>
+        <v>mlops</v>
       </c>
       <c r="F36" t="str">
-        <v>аналитик данных</v>
+        <v>mlops-инженер</v>
       </c>
       <c r="G36" t="str">
-        <v>SQL | Python</v>
+        <v>Docker | Kubernetes | Python</v>
       </c>
       <c r="H36" t="str">
-        <v>Data Analyst | аналитик данных | дата-аналитик</v>
+        <v>MLOps Engineer | ML Platform Engineer | mlops-инженер</v>
       </c>
       <c r="I36" t="str">
-        <v>data analyst | дата аналитик | аналитик данных | дата аналитика</v>
+        <v>mlops | ml ops | mlops engineer | ml платформа</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>BIAnalyst</v>
+        <v>NLP</v>
       </c>
       <c r="B37" t="str">
         <v>it</v>
@@ -1465,27 +1465,27 @@
         <v/>
       </c>
       <c r="D37" t="str">
-        <v/>
+        <v>hf</v>
       </c>
       <c r="E37" t="str">
-        <v>bi</v>
+        <v>nlp</v>
       </c>
       <c r="F37" t="str">
-        <v>bi-аналитик</v>
+        <v>nlp-инженер</v>
       </c>
       <c r="G37" t="str">
-        <v>SQL</v>
+        <v>Python</v>
       </c>
       <c r="H37" t="str">
-        <v>BI Analyst | Business Intelligence Analyst | bi-аналитик</v>
+        <v>NLP Engineer | Computational Linguist | nlp-инженер</v>
       </c>
       <c r="I37" t="str">
-        <v>bi analyst | би аналитик | business intelligence | bi аналитик | power bi | tableau</v>
+        <v>nlp engineer | nlp | обработка естественного языка | компьютерная лингвистика</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>AIResearcher</v>
+        <v>DataAnalyst</v>
       </c>
       <c r="B38" t="str">
         <v>it</v>
@@ -1494,27 +1494,27 @@
         <v/>
       </c>
       <c r="D38" t="str">
-        <v>hf</v>
+        <v>kaggle</v>
       </c>
       <c r="E38" t="str">
-        <v>research</v>
+        <v>data analyst</v>
       </c>
       <c r="F38" t="str">
-        <v>ai-исследователь</v>
+        <v>аналитик данных</v>
       </c>
       <c r="G38" t="str">
-        <v>Python</v>
+        <v>SQL | Python</v>
       </c>
       <c r="H38" t="str">
-        <v>AI Researcher | Research Scientist | Deep Learning Engineer</v>
+        <v>Data Analyst | аналитик данных | дата-аналитик</v>
       </c>
       <c r="I38" t="str">
-        <v>ai researcher | research scientist | ии исследователь | deep learning | llm engineer | prompt engineer</v>
+        <v>data analyst | дата аналитик | аналитик данных | дата аналитика</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>DevOps</v>
+        <v>BIAnalyst</v>
       </c>
       <c r="B39" t="str">
         <v>it</v>
@@ -1526,24 +1526,24 @@
         <v/>
       </c>
       <c r="E39" t="str">
-        <v>devops</v>
+        <v>bi</v>
       </c>
       <c r="F39" t="str">
-        <v>девопс инженер</v>
+        <v>bi-аналитик</v>
       </c>
       <c r="G39" t="str">
-        <v>Docker | Kubernetes</v>
+        <v>SQL</v>
       </c>
       <c r="H39" t="str">
-        <v>DevOps Engineer | SRE | Site Reliability Engineer | Platform Engineer | девопс инженер</v>
+        <v>BI Analyst | Business Intelligence Analyst | bi-аналитик</v>
       </c>
       <c r="I39" t="str">
-        <v>devops | девопс | sre | site reliability | platform engineer | infrastructure engineer | инженер инфраструктуры</v>
+        <v>bi analyst | би аналитик | business intelligence | bi аналитик | power bi | tableau</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Cloud</v>
+        <v>AIResearcher</v>
       </c>
       <c r="B40" t="str">
         <v>it</v>
@@ -1552,27 +1552,27 @@
         <v/>
       </c>
       <c r="D40" t="str">
-        <v/>
+        <v>hf</v>
       </c>
       <c r="E40" t="str">
-        <v>cloud engineer</v>
+        <v>research</v>
       </c>
       <c r="F40" t="str">
-        <v>облачный инженер</v>
+        <v>ai-исследователь</v>
       </c>
       <c r="G40" t="str">
-        <v>Kubernetes</v>
+        <v>Python</v>
       </c>
       <c r="H40" t="str">
-        <v>Cloud Engineer | Cloud Architect | инженер облачной инфраструктуры</v>
+        <v>AI Researcher | Research Scientist | Deep Learning Engineer</v>
       </c>
       <c r="I40" t="str">
-        <v>cloud engineer | cloud architect | облачный инженер | инженер облачной | aws engineer | azure engineer</v>
+        <v>ai researcher | research scientist | ии исследователь | deep learning | llm engineer | prompt engineer</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Network</v>
+        <v>DevOps</v>
       </c>
       <c r="B41" t="str">
         <v>it</v>
@@ -1584,24 +1584,24 @@
         <v/>
       </c>
       <c r="E41" t="str">
-        <v>network engineer</v>
+        <v>devops</v>
       </c>
       <c r="F41" t="str">
-        <v>сетевой инженер</v>
+        <v>девопс инженер</v>
       </c>
       <c r="G41" t="str">
-        <v/>
+        <v>Docker | Kubernetes</v>
       </c>
       <c r="H41" t="str">
-        <v>Network Engineer | Сетевой инженер | Network Administrator</v>
+        <v>DevOps Engineer | SRE | Site Reliability Engineer | Platform Engineer | девопс инженер</v>
       </c>
       <c r="I41" t="str">
-        <v>network engineer | сетевой инженер | сетевой администратор | network administrator | инженер сетей</v>
+        <v>devops | девопс | sre | site reliability | platform engineer | infrastructure engineer | инженер инфраструктуры</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>SysAdmin</v>
+        <v>Cloud</v>
       </c>
       <c r="B42" t="str">
         <v>it</v>
@@ -1613,24 +1613,24 @@
         <v/>
       </c>
       <c r="E42" t="str">
-        <v>system administrator</v>
+        <v>cloud engineer</v>
       </c>
       <c r="F42" t="str">
-        <v>системный администратор</v>
+        <v>облачный инженер</v>
       </c>
       <c r="G42" t="str">
-        <v/>
+        <v>Kubernetes</v>
       </c>
       <c r="H42" t="str">
-        <v>System Administrator | Системный администратор | Sysadmin</v>
+        <v>Cloud Engineer | Cloud Architect | инженер облачной инфраструктуры</v>
       </c>
       <c r="I42" t="str">
-        <v>системный администратор | system administrator | sysadmin | сисадмин | администратор серверов</v>
+        <v>cloud engineer | cloud architect | облачный инженер | инженер облачной | aws engineer | azure engineer</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>DBA</v>
+        <v>Network</v>
       </c>
       <c r="B43" t="str">
         <v>it</v>
@@ -1642,24 +1642,24 @@
         <v/>
       </c>
       <c r="E43" t="str">
-        <v>dba</v>
+        <v>network engineer</v>
       </c>
       <c r="F43" t="str">
-        <v>администратор баз данных</v>
+        <v>сетевой инженер</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Database Administrator | DBA | администратор баз данных</v>
+        <v>Network Engineer | Сетевой инженер | Network Administrator</v>
       </c>
       <c r="I43" t="str">
-        <v>администратор баз данных | database administrator |  dba  | oracle dba | postgres dba</v>
+        <v>network engineer | сетевой инженер | сетевой администратор | network administrator | инженер сетей</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>QA</v>
+        <v>SysAdmin</v>
       </c>
       <c r="B44" t="str">
         <v>it</v>
@@ -1671,24 +1671,24 @@
         <v/>
       </c>
       <c r="E44" t="str">
-        <v>qa engineer</v>
+        <v>system administrator</v>
       </c>
       <c r="F44" t="str">
-        <v>тестировщик</v>
+        <v>системный администратор</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>QA Engineer | Test Engineer | тестировщик | инженер по тестированию</v>
+        <v>System Administrator | Системный администратор | Sysadmin</v>
       </c>
       <c r="I44" t="str">
-        <v>qa engineer | тестировщик | инженер по тестированию | quality assurance | qa | ручное тестирование</v>
+        <v>системный администратор | system administrator | sysadmin | сисадмин | администратор серверов</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>QAAuto</v>
+        <v>WindowsEngineer</v>
       </c>
       <c r="B45" t="str">
         <v>it</v>
@@ -1700,24 +1700,24 @@
         <v/>
       </c>
       <c r="E45" t="str">
-        <v>sdet</v>
+        <v>windows</v>
       </c>
       <c r="F45" t="str">
-        <v>автотестировщик</v>
+        <v>windows-инженер</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>QA Automation | SDET | Automation Engineer | автотестировщик</v>
+        <v>Windows Engineer | Windows Administrator | инженер Windows</v>
       </c>
       <c r="I45" t="str">
-        <v>qa automation | automation qa | sdet | автотестировщик | автоматизатор тестирования | автотесты</v>
+        <v>windows engineer | windows администратор | windows инженер | инженер windows</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Security</v>
+        <v>StorageEngineer</v>
       </c>
       <c r="B46" t="str">
         <v>it</v>
@@ -1729,24 +1729,24 @@
         <v/>
       </c>
       <c r="E46" t="str">
-        <v>security</v>
+        <v>storage</v>
       </c>
       <c r="F46" t="str">
-        <v>специалист по информационной безопасности</v>
+        <v>инженер систем хранения</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Security Engineer | Information Security | AppSec Engineer | специалист по ИБ</v>
+        <v>Storage Engineer | инженер СХД</v>
       </c>
       <c r="I46" t="str">
-        <v>информационная безопасность | специалист по иб | application security | appsec | security engineer | безопасник</v>
+        <v>storage engineer | инженер схд | системы хранения | схд | storage</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Pentester</v>
+        <v>DataCenterEngineer</v>
       </c>
       <c r="B47" t="str">
         <v>it</v>
@@ -1758,24 +1758,24 @@
         <v/>
       </c>
       <c r="E47" t="str">
-        <v>penetration</v>
+        <v>data center</v>
       </c>
       <c r="F47" t="str">
-        <v>пентестер</v>
+        <v>инженер цод</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Penetration Tester | Ethical Hacker | пентестер</v>
+        <v>Data Center Engineer | инженер ЦОД</v>
       </c>
       <c r="I47" t="str">
-        <v>penetration tester | пентестер | pentest | этичный хакер | red team</v>
+        <v>data center | инженер цод |  цод  | дата центр | core engineering development</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>SystemAnalyst</v>
+        <v>MDMEngineer</v>
       </c>
       <c r="B48" t="str">
         <v>it</v>
@@ -1787,24 +1787,24 @@
         <v/>
       </c>
       <c r="E48" t="str">
-        <v>system analyst</v>
+        <v>master data</v>
       </c>
       <c r="F48" t="str">
-        <v>системный аналитик</v>
+        <v>mdm-инженер</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Системный аналитик | Systems Analyst</v>
+        <v>MDM Engineer | Master Data Management</v>
       </c>
       <c r="I48" t="str">
-        <v>системный аналитик | system analyst | systems analyst | системная аналитика</v>
+        <v>mdm engineer | master data management | mdm | управление мастер данными</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>BusinessAnalyst</v>
+        <v>DBA</v>
       </c>
       <c r="B49" t="str">
         <v>it</v>
@@ -1816,24 +1816,24 @@
         <v/>
       </c>
       <c r="E49" t="str">
-        <v>business analyst</v>
+        <v>dba</v>
       </c>
       <c r="F49" t="str">
-        <v>бизнес-аналитик</v>
+        <v>администратор баз данных</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Бизнес-аналитик | Business Analyst</v>
+        <v>Database Administrator | DBA | администратор баз данных</v>
       </c>
       <c r="I49" t="str">
-        <v>бизнес аналитик | business analyst | бизнес анализ</v>
+        <v>администратор баз данных | database administrator | database |  dba  | oracle dba | postgres dba | базы данных | база данных</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Analyst</v>
+        <v>QA</v>
       </c>
       <c r="B50" t="str">
         <v>it</v>
@@ -1845,24 +1845,24 @@
         <v/>
       </c>
       <c r="E50" t="str">
-        <v>analyst</v>
+        <v>qa engineer</v>
       </c>
       <c r="F50" t="str">
-        <v>аналитик</v>
+        <v>тестировщик</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Аналитик | Analyst</v>
+        <v>QA Engineer | Test Engineer | тестировщик | инженер по тестированию</v>
       </c>
       <c r="I50" t="str">
-        <v>аналитик | analyst</v>
+        <v>qa engineer | тестировщик | инженер по тестированию | quality assurance | qa | ручное тестирование | qa manual | qa front | qa load | qa mobile | performance | нагрузочное тестирование</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ProductAnalyst</v>
+        <v>QAAuto</v>
       </c>
       <c r="B51" t="str">
         <v>it</v>
@@ -1874,24 +1874,24 @@
         <v/>
       </c>
       <c r="E51" t="str">
-        <v>product analyst</v>
+        <v>sdet</v>
       </c>
       <c r="F51" t="str">
-        <v>продуктовый аналитик</v>
+        <v>автотестировщик</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Продуктовый аналитик | Product Analyst</v>
+        <v>QA Automation | SDET | Automation Engineer | автотестировщик</v>
       </c>
       <c r="I51" t="str">
-        <v>продуктовый аналитик | product analyst | продуктовая аналитика</v>
+        <v>qa automation | automation qa | sdet | автотестировщик | автоматизатор тестирования | автотесты | qa auto</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>PM</v>
+        <v>Security</v>
       </c>
       <c r="B52" t="str">
         <v>it</v>
@@ -1903,24 +1903,24 @@
         <v/>
       </c>
       <c r="E52" t="str">
-        <v>product manager</v>
+        <v>security</v>
       </c>
       <c r="F52" t="str">
-        <v>менеджер продукта</v>
+        <v>специалист по информационной безопасности</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Product Manager | Product Owner | продакт менеджер | продакт</v>
+        <v>Security Engineer | Information Security | AppSec Engineer | специалист по ИБ</v>
       </c>
       <c r="I52" t="str">
-        <v>product manager | продакт менеджер | продакт | product owner | продакт оунер | менеджер продукта</v>
+        <v>информационная безопасность | information security | специалист по иб | application security | appsec | security engineer | безопасн | кибербезопасность</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ProjectManager</v>
+        <v>Pentester</v>
       </c>
       <c r="B53" t="str">
         <v>it</v>
@@ -1932,24 +1932,24 @@
         <v/>
       </c>
       <c r="E53" t="str">
-        <v>project manager</v>
+        <v>penetration</v>
       </c>
       <c r="F53" t="str">
-        <v>проджект-менеджер</v>
+        <v>пентестер</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Project Manager | проджект менеджер | руководитель проекта</v>
+        <v>Penetration Tester | Ethical Hacker | пентестер</v>
       </c>
       <c r="I53" t="str">
-        <v>project manager | проджект менеджер | проджект | руководитель проекта | управление проектами</v>
+        <v>penetration tester | пентестер | pentest | этичный хакер | red team</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ScrumMaster</v>
+        <v>SystemAnalyst</v>
       </c>
       <c r="B54" t="str">
         <v>it</v>
@@ -1961,24 +1961,24 @@
         <v/>
       </c>
       <c r="E54" t="str">
-        <v>scrum master</v>
+        <v>system analyst</v>
       </c>
       <c r="F54" t="str">
-        <v>скрам-мастер</v>
+        <v>системный аналитик</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Scrum Master | Agile Coach | скрам-мастер</v>
+        <v>Системный аналитик | Systems Analyst</v>
       </c>
       <c r="I54" t="str">
-        <v>scrum master | скрам мастер | agile coach | аджайл коуч</v>
+        <v>системный аналитик | system analyst | systems analyst | системная аналитика</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Architect</v>
+        <v>BusinessAnalyst</v>
       </c>
       <c r="B55" t="str">
         <v>it</v>
@@ -1990,24 +1990,24 @@
         <v/>
       </c>
       <c r="E55" t="str">
-        <v>architect</v>
+        <v>business analyst</v>
       </c>
       <c r="F55" t="str">
-        <v>архитектор</v>
+        <v>бизнес-аналитик</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Solution Architect | Software Architect | System Architect | Архитектор ПО</v>
+        <v>Бизнес-аналитик | Business Analyst</v>
       </c>
       <c r="I55" t="str">
-        <v>solution architect | software architect | system architect | системный архитектор | архитектор по | архитектор решений</v>
+        <v>бизнес аналитик | business analyst | бизнес анализ | bpm аналитик</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>TechWriter</v>
+        <v>Analyst</v>
       </c>
       <c r="B56" t="str">
         <v>it</v>
@@ -2019,24 +2019,24 @@
         <v/>
       </c>
       <c r="E56" t="str">
-        <v>technical writer</v>
+        <v>analyst</v>
       </c>
       <c r="F56" t="str">
-        <v>технический писатель</v>
+        <v>аналитик</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Technical Writer | технический писатель | документатор</v>
+        <v>Аналитик | Analyst</v>
       </c>
       <c r="I56" t="str">
-        <v>technical writer | технический писатель | техписатель | documentation engineer</v>
+        <v>аналитик | analyst</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>DevRel</v>
+        <v>ProductAnalyst</v>
       </c>
       <c r="B57" t="str">
         <v>it</v>
@@ -2048,24 +2048,24 @@
         <v/>
       </c>
       <c r="E57" t="str">
-        <v>developer advocate</v>
+        <v>product analyst</v>
       </c>
       <c r="F57" t="str">
-        <v>devrel</v>
+        <v>продуктовый аналитик</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Developer Advocate | Developer Relations | DevRel</v>
+        <v>Продуктовый аналитик | Product Analyst</v>
       </c>
       <c r="I57" t="str">
-        <v>developer advocate | developer relations | devrel | деврел</v>
+        <v>продуктовый аналитик | product analyst | продуктовая аналитика</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>SupportEngineer</v>
+        <v>WebAnalyst</v>
       </c>
       <c r="B58" t="str">
         <v>it</v>
@@ -2077,24 +2077,24 @@
         <v/>
       </c>
       <c r="E58" t="str">
-        <v>support engineer</v>
+        <v>web analyst</v>
       </c>
       <c r="F58" t="str">
-        <v>инженер поддержки</v>
+        <v>веб-аналитик</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Support Engineer | Technical Support Engineer</v>
+        <v>Web Analyst | веб-аналитик | аналитик веб-аналитики</v>
       </c>
       <c r="I58" t="str">
-        <v>support engineer | инженер поддержки | инженер технической поддержки | l2 support | l3 support</v>
+        <v>web analyst | веб аналитик | web аналитик | веб аналитика</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ProductDesigner</v>
+        <v>PM</v>
       </c>
       <c r="B59" t="str">
         <v>it</v>
@@ -2103,27 +2103,27 @@
         <v/>
       </c>
       <c r="D59" t="str">
-        <v>behance | dribbble | dprofile</v>
+        <v/>
       </c>
       <c r="E59" t="str">
-        <v/>
+        <v>product manager</v>
       </c>
       <c r="F59" t="str">
-        <v>продуктовый дизайнер</v>
+        <v>менеджер продукта</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Product Designer | UX/UI Designer | UX Designer | UI Designer | продуктовый дизайнер</v>
+        <v>Product Manager | Product Owner | продакт менеджер | продакт</v>
       </c>
       <c r="I59" t="str">
-        <v>product designer | продуктовый дизайнер | ux designer | ui designer | ux ui | ux дизайнер | ui дизайнер | дизайнер интерфейсов</v>
+        <v>product manager | продакт менеджер | продакт | product owner | продакт оунер | менеджер продукта | technical product manager | ml product manager</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>UXResearcher</v>
+        <v>ProjectManager</v>
       </c>
       <c r="B60" t="str">
         <v>it</v>
@@ -2132,204 +2132,204 @@
         <v/>
       </c>
       <c r="D60" t="str">
-        <v>dprofile</v>
+        <v/>
       </c>
       <c r="E60" t="str">
-        <v/>
+        <v>project manager</v>
       </c>
       <c r="F60" t="str">
-        <v>ux-исследователь</v>
+        <v>проджект-менеджер</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>UX Researcher | User Researcher | ux-исследователь</v>
+        <v>Project Manager | проджект менеджер | руководитель проекта</v>
       </c>
       <c r="I60" t="str">
-        <v>ux researcher | ux исследователь | user researcher | юзабилити</v>
+        <v>project manager | проджект менеджер | проджект | руководитель проекта | управление проектами | it project manager</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>CEO</v>
+        <v>ReleaseManager</v>
       </c>
       <c r="B61" t="str">
-        <v>nonit</v>
+        <v>it</v>
       </c>
       <c r="C61" t="str">
-        <v>exec</v>
+        <v/>
       </c>
       <c r="D61" t="str">
         <v/>
       </c>
       <c r="E61" t="str">
-        <v/>
+        <v>release manager</v>
       </c>
       <c r="F61" t="str">
-        <v>генеральный директор</v>
+        <v>релиз-менеджер</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>CEO | Chief Executive Officer | генеральный директор | Managing Director</v>
+        <v>Release Manager | менеджер выпуска | релиз-менеджер</v>
       </c>
       <c r="I61" t="str">
-        <v>ceo | chief executive officer | генеральный директор | гендиректор | управляющий директор</v>
+        <v>release manager | менеджер выпуска | релиз менеджер | управление релизами</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>CFO</v>
+        <v>ScrumMaster</v>
       </c>
       <c r="B62" t="str">
-        <v>nonit</v>
+        <v>it</v>
       </c>
       <c r="C62" t="str">
-        <v>exec</v>
+        <v/>
       </c>
       <c r="D62" t="str">
         <v/>
       </c>
       <c r="E62" t="str">
-        <v/>
+        <v>scrum master</v>
       </c>
       <c r="F62" t="str">
-        <v>финансовый директор</v>
+        <v>скрам-мастер</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>CFO | Chief Financial Officer | финансовый директор</v>
+        <v>Scrum Master | Agile Coach | скрам-мастер</v>
       </c>
       <c r="I62" t="str">
-        <v>cfo | chief financial officer | финансовый директор | фин директор</v>
+        <v>scrum master | скрам мастер | agile coach | аджайл коуч</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>COO</v>
+        <v>Architect</v>
       </c>
       <c r="B63" t="str">
-        <v>nonit</v>
+        <v>it</v>
       </c>
       <c r="C63" t="str">
-        <v>exec</v>
+        <v/>
       </c>
       <c r="D63" t="str">
         <v/>
       </c>
       <c r="E63" t="str">
-        <v/>
+        <v>architect</v>
       </c>
       <c r="F63" t="str">
-        <v>операционный директор</v>
+        <v>архитектор</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>COO | Chief Operating Officer | операционный директор</v>
+        <v>Solution Architect | Software Architect | System Architect | Архитектор ПО</v>
       </c>
       <c r="I63" t="str">
-        <v>coo | chief operating officer | операционный директор</v>
+        <v>solution architect | software architect | system architect | системный архитектор | архитектор по | архитектор решений | архитектор телеком</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>CMO</v>
+        <v>TechWriter</v>
       </c>
       <c r="B64" t="str">
-        <v>nonit</v>
+        <v>it</v>
       </c>
       <c r="C64" t="str">
-        <v>exec</v>
+        <v/>
       </c>
       <c r="D64" t="str">
         <v/>
       </c>
       <c r="E64" t="str">
-        <v/>
+        <v>technical writer</v>
       </c>
       <c r="F64" t="str">
-        <v>директор по маркетингу</v>
+        <v>технический писатель</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>CMO | Chief Marketing Officer | директор по маркетингу</v>
+        <v>Technical Writer | технический писатель | документатор</v>
       </c>
       <c r="I64" t="str">
-        <v>cmo | chief marketing officer | директор по маркетингу | маркетинг директор</v>
+        <v>technical writer | технический писатель | техписатель | documentation engineer</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>HRD</v>
+        <v>DevRel</v>
       </c>
       <c r="B65" t="str">
-        <v>nonit</v>
+        <v>it</v>
       </c>
       <c r="C65" t="str">
-        <v>exec</v>
+        <v/>
       </c>
       <c r="D65" t="str">
         <v/>
       </c>
       <c r="E65" t="str">
-        <v/>
+        <v>developer advocate</v>
       </c>
       <c r="F65" t="str">
-        <v>директор по персоналу</v>
+        <v>devrel</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>HRD | CHRO | HR Director | директор по персоналу</v>
+        <v>Developer Advocate | Developer Relations | DevRel</v>
       </c>
       <c r="I65" t="str">
-        <v>chro | hrd | hr director | директор по персоналу | hr директор</v>
+        <v>developer advocate | developer relations | devrel | деврел</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Commercial</v>
+        <v>SupportEngineer</v>
       </c>
       <c r="B66" t="str">
-        <v>nonit</v>
+        <v>it</v>
       </c>
       <c r="C66" t="str">
-        <v>exec</v>
+        <v/>
       </c>
       <c r="D66" t="str">
         <v/>
       </c>
       <c r="E66" t="str">
-        <v/>
+        <v>support engineer</v>
       </c>
       <c r="F66" t="str">
-        <v>коммерческий директор</v>
+        <v>инженер поддержки</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Коммерческий директор | Commercial Director | CCO</v>
+        <v>Support Engineer | Technical Support Engineer | 2nd/3rd Line Support</v>
       </c>
       <c r="I66" t="str">
-        <v>коммерческий директор | commercial director | cco | директор по продажам</v>
+        <v>support engineer | инженер поддержки | инженер технической поддержки | l2 support | l3 support | 2nd line | 3rd line | вторая линия | третья линия | тех сопровождение | техническое сопровождение | сопровождени</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Marketing</v>
+        <v>GovTech</v>
       </c>
       <c r="B67" t="str">
-        <v>nonit</v>
+        <v>it</v>
       </c>
       <c r="C67" t="str">
         <v/>
@@ -2338,88 +2338,88 @@
         <v/>
       </c>
       <c r="E67" t="str">
-        <v/>
+        <v>govtech</v>
       </c>
       <c r="F67" t="str">
-        <v>маркетолог</v>
+        <v>цифровые госсервисы</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Маркетолог | Интернет-маркетолог | Digital Marketing</v>
+        <v>GovTech | Цифровые государственные сервисы | гос.технологии</v>
       </c>
       <c r="I67" t="str">
-        <v>маркетолог | интернет маркетолог | digital marketing | диджитал маркетолог | маркетинг</v>
+        <v>govtech | цифровые государственные сервисы | гос технологии | гос.технологии | гостех | госсервисы | государственные сервисы</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>SMM</v>
+        <v>ProductDesigner</v>
       </c>
       <c r="B68" t="str">
-        <v>nonit</v>
+        <v>it</v>
       </c>
       <c r="C68" t="str">
         <v/>
       </c>
       <c r="D68" t="str">
-        <v/>
+        <v>behance | dribbble | dprofile</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>smm-менеджер</v>
+        <v>продуктовый дизайнер</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>SMM-менеджер | Social Media Manager | контент-мейкер</v>
+        <v>Product Designer | UX/UI Designer | UX Designer | UI Designer | продуктовый дизайнер</v>
       </c>
       <c r="I68" t="str">
-        <v>smm | smm менеджер | social media | сммщик | таргетолог</v>
+        <v>product designer | продуктовый дизайнер | продуктовый дизайн | ux designer | ui designer | ux ui | ux дизайнер | ui дизайнер | дизайнер интерфейсов</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>SEO</v>
+        <v>UXResearcher</v>
       </c>
       <c r="B69" t="str">
-        <v>nonit</v>
+        <v>it</v>
       </c>
       <c r="C69" t="str">
         <v/>
       </c>
       <c r="D69" t="str">
-        <v/>
+        <v>dprofile</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>seo-специалист</v>
+        <v>ux-исследователь</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>SEO-специалист | SEO Specialist | поисковый оптимизатор</v>
+        <v>UX Researcher | User Researcher | ux-исследователь</v>
       </c>
       <c r="I69" t="str">
-        <v>seo | seo специалист | сео | поисковая оптимизация | сеошник</v>
+        <v>ux researcher | ux исследователь | user researcher | юзабилити | исследования интерфейсов</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>PPC</v>
+        <v>CEO</v>
       </c>
       <c r="B70" t="str">
         <v>nonit</v>
       </c>
       <c r="C70" t="str">
-        <v/>
+        <v>exec</v>
       </c>
       <c r="D70" t="str">
         <v/>
@@ -2428,27 +2428,27 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>специалист по контекстной рекламе</v>
+        <v>генеральный директор</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>PPC Specialist | Специалист по контекстной рекламе | Директолог</v>
+        <v>CEO | Chief Executive Officer | генеральный директор | Managing Director</v>
       </c>
       <c r="I70" t="str">
-        <v>ppc | контекстная реклама | контекстолог | директолог | специалист по рекламе</v>
+        <v>ceo | chief executive officer | генеральный директор | гендиректор | управляющий директор</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>PR</v>
+        <v>CFO</v>
       </c>
       <c r="B71" t="str">
         <v>nonit</v>
       </c>
       <c r="C71" t="str">
-        <v/>
+        <v>exec</v>
       </c>
       <c r="D71" t="str">
         <v/>
@@ -2457,27 +2457,27 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>pr-менеджер</v>
+        <v>финансовый директор</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>PR-менеджер | PR Manager | Public Relations</v>
+        <v>CFO | Chief Financial Officer | финансовый директор</v>
       </c>
       <c r="I71" t="str">
-        <v>pr менеджер | пиар | public relations | связям с общественностью | pr manager</v>
+        <v>cfo | chief financial officer | финансовый директор | фин директор</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>BrandManager</v>
+        <v>COO</v>
       </c>
       <c r="B72" t="str">
         <v>nonit</v>
       </c>
       <c r="C72" t="str">
-        <v/>
+        <v>exec</v>
       </c>
       <c r="D72" t="str">
         <v/>
@@ -2486,27 +2486,27 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>бренд-менеджер</v>
+        <v>операционный директор</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Бренд-менеджер | Brand Manager</v>
+        <v>COO | Chief Operating Officer | операционный директор</v>
       </c>
       <c r="I72" t="str">
-        <v>бренд менеджер | brand manager | управление брендом</v>
+        <v>coo | chief operating officer | операционный директор</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Content</v>
+        <v>CMO</v>
       </c>
       <c r="B73" t="str">
         <v>nonit</v>
       </c>
       <c r="C73" t="str">
-        <v/>
+        <v>exec</v>
       </c>
       <c r="D73" t="str">
         <v/>
@@ -2515,21 +2515,21 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>копирайтер</v>
+        <v>директор по маркетингу</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Копирайтер | Контент-менеджер | Редактор | Технический писатель</v>
+        <v>CMO | Chief Marketing Officer | директор по маркетингу</v>
       </c>
       <c r="I73" t="str">
-        <v>копирайтер | copywriter | контент менеджер | content manager | редактор | автор текстов | контент</v>
+        <v>cmo | chief marketing officer | директор по маркетингу | маркетинг директор</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Sales</v>
+        <v>HRD</v>
       </c>
       <c r="B74" t="str">
         <v>nonit</v>
@@ -2544,21 +2544,21 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>менеджер по продажам</v>
+        <v>директор по персоналу</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Менеджер по продажам | Sales Manager | Account Manager | Руководитель отдела продаж</v>
+        <v>HRD | CHRO | HR Director | директор по персоналу</v>
       </c>
       <c r="I74" t="str">
-        <v>менеджер по продажам | sales manager | account manager | аккаунт менеджер | руководитель отдела продаж | роп | продажи</v>
+        <v>chro | hrd | hr director | директор по персоналу | hr директор</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>KAM</v>
+        <v>Commercial</v>
       </c>
       <c r="B75" t="str">
         <v>nonit</v>
@@ -2573,21 +2573,21 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>менеджер по работе с ключевыми клиентами</v>
+        <v>коммерческий директор</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Key Account Manager | KAM | менеджер по ключевым клиентам</v>
+        <v>Коммерческий директор | Commercial Director | CCO</v>
       </c>
       <c r="I75" t="str">
-        <v>key account | kam | ключевые клиенты | менеджер по ключевым клиентам</v>
+        <v>коммерческий директор | commercial director | cco | директор по продажам</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>BizDev</v>
+        <v>Management</v>
       </c>
       <c r="B76" t="str">
         <v>nonit</v>
@@ -2602,21 +2602,21 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>менеджер по развитию бизнеса</v>
+        <v>руководитель</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Business Development Manager | BizDev | развитие бизнеса</v>
+        <v>General Manager | Руководитель | Директор | управляющий</v>
       </c>
       <c r="I76" t="str">
-        <v>business development | bizdev | биздев | развитие бизнеса | менеджер по развитию</v>
+        <v>general manager | управление | управляющий | общекорпоративное развитие | руководитель направления | руководитель подразделения</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Accountant</v>
+        <v>Marketing</v>
       </c>
       <c r="B77" t="str">
         <v>nonit</v>
@@ -2631,21 +2631,21 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>бухгалтер</v>
+        <v>маркетолог</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Бухгалтер | Главный бухгалтер | Accountant</v>
+        <v>Маркетолог | Интернет-маркетолог | Digital Marketing</v>
       </c>
       <c r="I77" t="str">
-        <v>бухгалтер | accountant | главный бухгалтер | главбух | бухгалтерия</v>
+        <v>маркетолог | интернет маркетолог | digital marketing | диджитал маркетолог | маркетинг | маркетинговые коммуникации | онлайн привлечение | маркетинговый аналитик</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>FinAnalyst</v>
+        <v>SMM</v>
       </c>
       <c r="B78" t="str">
         <v>nonit</v>
@@ -2660,21 +2660,21 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>финансовый аналитик</v>
+        <v>smm-менеджер</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Финансовый аналитик | Financial Analyst</v>
+        <v>SMM-менеджер | Social Media Manager | контент-мейкер</v>
       </c>
       <c r="I78" t="str">
-        <v>финансовый аналитик | financial analyst | финансовая аналитика</v>
+        <v>smm | smm менеджер | social media | сммщик</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Auditor</v>
+        <v>Targetolog</v>
       </c>
       <c r="B79" t="str">
         <v>nonit</v>
@@ -2689,21 +2689,21 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>аудитор</v>
+        <v>таргетолог</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Аудитор | Auditor | внутренний аудит</v>
+        <v>Таргетолог | Targeting Specialist | специалист по таргетированной рекламе</v>
       </c>
       <c r="I79" t="str">
-        <v>аудитор | auditor | аудит | внутренний аудит</v>
+        <v>таргетолог | таргетированная реклама | таргет | target</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Economist</v>
+        <v>SEO</v>
       </c>
       <c r="B80" t="str">
         <v>nonit</v>
@@ -2718,21 +2718,21 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>экономист</v>
+        <v>seo-специалист</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Экономист | Economist | планово-экономический</v>
+        <v>SEO-специалист | SEO Specialist | поисковый оптимизатор</v>
       </c>
       <c r="I80" t="str">
-        <v>экономист | economist | планирование бюджета</v>
+        <v>seo | seo специалист | сео | поисковая оптимизация | поисковое продвижение | сеошник</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Recruiter</v>
+        <v>PPC</v>
       </c>
       <c r="B81" t="str">
         <v>nonit</v>
@@ -2747,21 +2747,21 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>рекрутер</v>
+        <v>специалист по контекстной рекламе</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Рекрутер | IT-рекрутер | Talent Acquisition | Sourcer</v>
+        <v>PPC Specialist | Специалист по контекстной рекламе | Директолог</v>
       </c>
       <c r="I81" t="str">
-        <v>рекрутер | recruiter | it рекрутер | talent acquisition | сорсер | sourcer | подбор персонала</v>
+        <v>ppc | контекстная реклама | контекстная и медийная реклама | медийная реклама | контекстолог | директолог | специалист по рекламе | performance marketing | перформанс</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>HRManager</v>
+        <v>Influence</v>
       </c>
       <c r="B82" t="str">
         <v>nonit</v>
@@ -2776,21 +2776,21 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>hr-менеджер</v>
+        <v>менеджер по работе с блогерами</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>HR-менеджер | HR Generalist | менеджер по персоналу</v>
+        <v>Influencer Marketing Manager | Менеджер по работе с блогерами</v>
       </c>
       <c r="I82" t="str">
-        <v>hr менеджер | эйчар | менеджер по персоналу |  hr  | human resources</v>
+        <v>работа с блогерами | инфлюенс | influencer marketing | блогеры | инфлюенсер</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>HRBP</v>
+        <v>PR</v>
       </c>
       <c r="B83" t="str">
         <v>nonit</v>
@@ -2805,21 +2805,21 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>hr бизнес-партнёр</v>
+        <v>pr-менеджер</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>HR Business Partner | HRBP</v>
+        <v>PR-менеджер | PR Manager | Public Relations</v>
       </c>
       <c r="I83" t="str">
-        <v>hrbp | hr бизнес партнер | hr business partner</v>
+        <v>pr менеджер |  pr  | пиар | public relations | связям с общественностью | связи с общественностью | pr manager</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>CnB</v>
+        <v>SERM</v>
       </c>
       <c r="B84" t="str">
         <v>nonit</v>
@@ -2834,21 +2834,21 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>специалист по компенсациям и льготам</v>
+        <v>специалист по репутации</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>C&amp;B Specialist | Compensation &amp; Benefits | специалист по C&amp;B</v>
+        <v>SERM Specialist | Репутационный маркетинг | ORM</v>
       </c>
       <c r="I84" t="str">
-        <v>c&amp;b | компенсации и льготы | compensation | benefits | кадровое администрирование</v>
+        <v>serm | репутационный маркетинг | orm | управление репутацией</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Lawyer</v>
+        <v>BrandManager</v>
       </c>
       <c r="B85" t="str">
         <v>nonit</v>
@@ -2863,21 +2863,21 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>юрист</v>
+        <v>бренд-менеджер</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Юрист | Юрисконсульт | Legal Counsel | Корпоративный юрист</v>
+        <v>Бренд-менеджер | Brand Manager</v>
       </c>
       <c r="I85" t="str">
-        <v>юрист | юрисконсульт | legal counsel | lawyer | адвокат | корпоративный юрист | правовое сопровождение</v>
+        <v>бренд менеджер | brand manager | управление брендом</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Procurement</v>
+        <v>Event</v>
       </c>
       <c r="B86" t="str">
         <v>nonit</v>
@@ -2892,21 +2892,21 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>специалист по закупкам</v>
+        <v>event-менеджер</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Специалист по закупкам | Procurement Manager | Категорийный менеджер</v>
+        <v>Event Manager | Ивент-менеджер | организатор мероприятий</v>
       </c>
       <c r="I86" t="str">
-        <v>закупки | специалист по закупкам | procurement | снабжение | менеджер по закупкам | категорийный менеджер</v>
+        <v>event manager | ивент | ивент маркетинг | event маркетинг | организатор мероприятий</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Logistics</v>
+        <v>Content</v>
       </c>
       <c r="B87" t="str">
         <v>nonit</v>
@@ -2915,27 +2915,27 @@
         <v/>
       </c>
       <c r="D87" t="str">
-        <v>logist</v>
+        <v/>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>логист</v>
+        <v>копирайтер</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Логист | Менеджер по логистике | Специалист по ВЭД | Supply Chain Manager</v>
+        <v>Копирайтер | Контент-менеджер | Редактор | Технический писатель</v>
       </c>
       <c r="I87" t="str">
-        <v>логист | логистика | менеджер по логистике | вэд | специалист по вэд | supply chain | цепочки поставок</v>
+        <v>копирайтер | copywriter | контент менеджер | content manager | редактор | редактура | автор текстов | контент | ux редактор | линейный редактор</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Warehouse</v>
+        <v>Producer</v>
       </c>
       <c r="B88" t="str">
         <v>nonit</v>
@@ -2944,27 +2944,27 @@
         <v/>
       </c>
       <c r="D88" t="str">
-        <v>logist</v>
+        <v/>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>заведующий складом</v>
+        <v>продюсер</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Начальник склада | Заведующий складом | Warehouse Manager</v>
+        <v>Продюсер | Producer | Видеопродюсер</v>
       </c>
       <c r="I88" t="str">
-        <v>начальник склада | заведующий складом | warehouse | складская логистика | кладовщик</v>
+        <v>продюсер | producer | видеопродюсер | контент продюсер</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Support</v>
+        <v>Director</v>
       </c>
       <c r="B89" t="str">
         <v>nonit</v>
@@ -2979,21 +2979,21 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>специалист поддержки</v>
+        <v>режиссёр</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Специалист поддержки | Customer Support | Service Desk</v>
+        <v>Режиссёр | Director | Режиссёр монтажа</v>
       </c>
       <c r="I89" t="str">
-        <v>специалист поддержки | customer support | техподдержка | служба поддержки | helpdesk | саппорт | поддержк</v>
+        <v>режиссер | режиссёр | director | режиссер монтажа</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>CustomerSuccess</v>
+        <v>VideoStudio</v>
       </c>
       <c r="B90" t="str">
         <v>nonit</v>
@@ -3008,21 +3008,21 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>менеджер по работе с клиентами</v>
+        <v>видеограф</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Customer Success Manager | Account Manager | менеджер по клиентам</v>
+        <v>Видеограф | Video Editor | специалист видеостудии</v>
       </c>
       <c r="I90" t="str">
-        <v>customer success | csm | менеджер по работе с клиентами | клиентский сервис</v>
+        <v>видеограф | видеомонтаж | видеостуди | видеооператор | video editor | монтажер</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>OfficeManager</v>
+        <v>MediaManager</v>
       </c>
       <c r="B91" t="str">
         <v>nonit</v>
@@ -3037,50 +3037,1152 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>офис-менеджер</v>
+        <v>менеджер по медиа</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Офис-менеджер | Office Manager | Административный помощник</v>
+        <v>Media Manager | Медиабаер | менеджер по работе с медиа</v>
       </c>
       <c r="I91" t="str">
-        <v>офис менеджер | office manager | администратор офиса | ассистент руководителя | секретарь</v>
+        <v>управление медиа | медиабаинг | медиабаер | работа с медиа | медиаменеджер | media buying</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
+        <v>Distribution</v>
+      </c>
+      <c r="B92" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C92" t="str">
+        <v/>
+      </c>
+      <c r="D92" t="str">
+        <v/>
+      </c>
+      <c r="E92" t="str">
+        <v/>
+      </c>
+      <c r="F92" t="str">
+        <v>менеджер по дистрибуции</v>
+      </c>
+      <c r="G92" t="str">
+        <v/>
+      </c>
+      <c r="H92" t="str">
+        <v>Distribution Manager | менеджер по дистрибуции</v>
+      </c>
+      <c r="I92" t="str">
+        <v>дистрибуция | distribution | дистрибьютор | менеджер по дистрибуции</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>Localization</v>
+      </c>
+      <c r="B93" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C93" t="str">
+        <v/>
+      </c>
+      <c r="D93" t="str">
+        <v/>
+      </c>
+      <c r="E93" t="str">
+        <v/>
+      </c>
+      <c r="F93" t="str">
+        <v>специалист по локализации</v>
+      </c>
+      <c r="G93" t="str">
+        <v/>
+      </c>
+      <c r="H93" t="str">
+        <v>Localization Specialist | Переводчик | менеджер локализации</v>
+      </c>
+      <c r="I93" t="str">
+        <v>локализация | localization | переводчик | локализатор</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>CXResearch</v>
+      </c>
+      <c r="B94" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C94" t="str">
+        <v/>
+      </c>
+      <c r="D94" t="str">
+        <v/>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
+        <v>исследователь клиентского опыта</v>
+      </c>
+      <c r="G94" t="str">
+        <v/>
+      </c>
+      <c r="H94" t="str">
+        <v>CX Researcher | Customer Experience Researcher | аналитик CX</v>
+      </c>
+      <c r="I94" t="str">
+        <v>cx исследования | customer experience | аналитик cx | клиентский опыт | cx research | cx аналитик</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="B95" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C95" t="str">
+        <v>exec</v>
+      </c>
+      <c r="D95" t="str">
+        <v/>
+      </c>
+      <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" t="str">
+        <v>менеджер по продажам</v>
+      </c>
+      <c r="G95" t="str">
+        <v/>
+      </c>
+      <c r="H95" t="str">
+        <v>Менеджер по продажам | Sales Manager | Account Manager | Руководитель отдела продаж</v>
+      </c>
+      <c r="I95" t="str">
+        <v>менеджер по продажам | sales manager | account manager | аккаунт менеджер | руководитель отдела продаж | роп | продажи | развитие продаж</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>KAM</v>
+      </c>
+      <c r="B96" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C96" t="str">
+        <v>exec</v>
+      </c>
+      <c r="D96" t="str">
+        <v/>
+      </c>
+      <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
+        <v>менеджер по работе с ключевыми клиентами</v>
+      </c>
+      <c r="G96" t="str">
+        <v/>
+      </c>
+      <c r="H96" t="str">
+        <v>Key Account Manager | KAM | менеджер по ключевым клиентам</v>
+      </c>
+      <c r="I96" t="str">
+        <v>key account | kam | ключевые клиенты | менеджер по ключевым клиентам</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>BizDev</v>
+      </c>
+      <c r="B97" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C97" t="str">
+        <v>exec</v>
+      </c>
+      <c r="D97" t="str">
+        <v/>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
+        <v>менеджер по развитию бизнеса</v>
+      </c>
+      <c r="G97" t="str">
+        <v/>
+      </c>
+      <c r="H97" t="str">
+        <v>Business Development Manager | BizDev | развитие бизнеса</v>
+      </c>
+      <c r="I97" t="str">
+        <v>business development | bizdev | биздев | развитие бизнеса | менеджер по развитию</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>CustomerSuccess</v>
+      </c>
+      <c r="B98" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C98" t="str">
+        <v/>
+      </c>
+      <c r="D98" t="str">
+        <v/>
+      </c>
+      <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
+        <v>менеджер по работе с клиентами</v>
+      </c>
+      <c r="G98" t="str">
+        <v/>
+      </c>
+      <c r="H98" t="str">
+        <v>Customer Success Manager | Account Manager | менеджер по клиентам</v>
+      </c>
+      <c r="I98" t="str">
+        <v>customer success | csm | менеджер по работе с клиентами | клиентский сервис | управление клиентским сервисом | развитие сервиса</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>Accountant</v>
+      </c>
+      <c r="B99" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C99" t="str">
+        <v/>
+      </c>
+      <c r="D99" t="str">
+        <v/>
+      </c>
+      <c r="E99" t="str">
+        <v/>
+      </c>
+      <c r="F99" t="str">
+        <v>бухгалтер</v>
+      </c>
+      <c r="G99" t="str">
+        <v/>
+      </c>
+      <c r="H99" t="str">
+        <v>Бухгалтер | Главный бухгалтер | Accountant</v>
+      </c>
+      <c r="I99" t="str">
+        <v>бухгалтер | accountant | главный бухгалтер | главбух | бухгалтерия</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>FinAnalyst</v>
+      </c>
+      <c r="B100" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C100" t="str">
+        <v/>
+      </c>
+      <c r="D100" t="str">
+        <v/>
+      </c>
+      <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" t="str">
+        <v>финансовый аналитик</v>
+      </c>
+      <c r="G100" t="str">
+        <v/>
+      </c>
+      <c r="H100" t="str">
+        <v>Финансовый аналитик | Financial Analyst | финансовый аналитик данных</v>
+      </c>
+      <c r="I100" t="str">
+        <v>финансовый аналитик | financial analyst | финансовая аналитика | финансовый аналитик данных</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="B101" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C101" t="str">
+        <v/>
+      </c>
+      <c r="D101" t="str">
+        <v/>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
+        <v>финансовый менеджер</v>
+      </c>
+      <c r="G101" t="str">
+        <v/>
+      </c>
+      <c r="H101" t="str">
+        <v>Финансовый менеджер | Finance Manager | Финансовый бизнес-партнёр</v>
+      </c>
+      <c r="I101" t="str">
+        <v>финансы | финансовый менеджер | финансовый бизнес партнер | finance | финансист | корпоративное финансирование</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>Auditor</v>
+      </c>
+      <c r="B102" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C102" t="str">
+        <v/>
+      </c>
+      <c r="D102" t="str">
+        <v/>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
+        <v>аудитор</v>
+      </c>
+      <c r="G102" t="str">
+        <v/>
+      </c>
+      <c r="H102" t="str">
+        <v>Аудитор | Auditor | внутренний аудит</v>
+      </c>
+      <c r="I102" t="str">
+        <v>аудитор | auditor | аудит | внутренний аудит | ит аудит</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Economist</v>
+      </c>
+      <c r="B103" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C103" t="str">
+        <v/>
+      </c>
+      <c r="D103" t="str">
+        <v/>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
+        <v>экономист</v>
+      </c>
+      <c r="G103" t="str">
+        <v/>
+      </c>
+      <c r="H103" t="str">
+        <v>Экономист | Economist | планово-экономический</v>
+      </c>
+      <c r="I103" t="str">
+        <v>экономист | economist | планирование бюджета</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Tax</v>
+      </c>
+      <c r="B104" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C104" t="str">
+        <v/>
+      </c>
+      <c r="D104" t="str">
+        <v/>
+      </c>
+      <c r="E104" t="str">
+        <v/>
+      </c>
+      <c r="F104" t="str">
+        <v>налоговый специалист</v>
+      </c>
+      <c r="G104" t="str">
+        <v/>
+      </c>
+      <c r="H104" t="str">
+        <v>Налоговый менеджер | Tax Manager | налоговый консультант</v>
+      </c>
+      <c r="I104" t="str">
+        <v>налоги | налоговый | tax | налогообложение | налоговый консультант</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>Treasury</v>
+      </c>
+      <c r="B105" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C105" t="str">
+        <v/>
+      </c>
+      <c r="D105" t="str">
+        <v/>
+      </c>
+      <c r="E105" t="str">
+        <v/>
+      </c>
+      <c r="F105" t="str">
+        <v>казначей</v>
+      </c>
+      <c r="G105" t="str">
+        <v/>
+      </c>
+      <c r="H105" t="str">
+        <v>Казначей | Treasury Manager | специалист казначейства</v>
+      </c>
+      <c r="I105" t="str">
+        <v>казначейство | казначей | treasury | технология расчетов</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>Actuary</v>
+      </c>
+      <c r="B106" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C106" t="str">
+        <v/>
+      </c>
+      <c r="D106" t="str">
+        <v/>
+      </c>
+      <c r="E106" t="str">
+        <v/>
+      </c>
+      <c r="F106" t="str">
+        <v>актуарий</v>
+      </c>
+      <c r="G106" t="str">
+        <v/>
+      </c>
+      <c r="H106" t="str">
+        <v>Актуарий | Actuary</v>
+      </c>
+      <c r="I106" t="str">
+        <v>актуарий | actuary | актуарии | актуарные расчеты</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>Investment</v>
+      </c>
+      <c r="B107" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C107" t="str">
+        <v>exec</v>
+      </c>
+      <c r="D107" t="str">
+        <v/>
+      </c>
+      <c r="E107" t="str">
+        <v/>
+      </c>
+      <c r="F107" t="str">
+        <v>инвестиционный менеджер</v>
+      </c>
+      <c r="G107" t="str">
+        <v/>
+      </c>
+      <c r="H107" t="str">
+        <v>Investment Manager | Инвестиционный аналитик | инвестиционный консультант</v>
+      </c>
+      <c r="I107" t="str">
+        <v>инвестиции | инвестиционный | investment | инвестиционное консультирование | развитие инвестиционных продуктов | инвестиционный аналитик</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>Trader</v>
+      </c>
+      <c r="B108" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C108" t="str">
+        <v/>
+      </c>
+      <c r="D108" t="str">
+        <v/>
+      </c>
+      <c r="E108" t="str">
+        <v/>
+      </c>
+      <c r="F108" t="str">
+        <v>трейдер</v>
+      </c>
+      <c r="G108" t="str">
+        <v/>
+      </c>
+      <c r="H108" t="str">
+        <v>Трейдер | Trader | Дилер</v>
+      </c>
+      <c r="I108" t="str">
+        <v>трейдер | trader | трейдинг | дилер | трейдеры инвестиций</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>Risk</v>
+      </c>
+      <c r="B109" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C109" t="str">
+        <v/>
+      </c>
+      <c r="D109" t="str">
+        <v/>
+      </c>
+      <c r="E109" t="str">
+        <v/>
+      </c>
+      <c r="F109" t="str">
+        <v>риск-менеджер</v>
+      </c>
+      <c r="G109" t="str">
+        <v/>
+      </c>
+      <c r="H109" t="str">
+        <v>Риск-менеджер | Risk Manager | риск-аналитик</v>
+      </c>
+      <c r="I109" t="str">
+        <v>риск менеджер | risk manager | риск менеджмент | банковский риск | кредитный риск | управление рисками</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>Compliance</v>
+      </c>
+      <c r="B110" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C110" t="str">
+        <v/>
+      </c>
+      <c r="D110" t="str">
+        <v/>
+      </c>
+      <c r="E110" t="str">
+        <v/>
+      </c>
+      <c r="F110" t="str">
+        <v>комплаенс-менеджер</v>
+      </c>
+      <c r="G110" t="str">
+        <v/>
+      </c>
+      <c r="H110" t="str">
+        <v>Compliance Manager | Комплаенс | специалист по комплаенс</v>
+      </c>
+      <c r="I110" t="str">
+        <v>compliance | комплаенс | антикоррупционный | этический комплаенс | управление compliance | lmc | нормативное сопровождение | регуляторная отчетность | контроль режима санкций | внутренний контроль | свк | финансовый мониторинг | анализ сомнительных операций | kyc | aml</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>BankOps</v>
+      </c>
+      <c r="B111" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C111" t="str">
+        <v/>
+      </c>
+      <c r="D111" t="str">
+        <v/>
+      </c>
+      <c r="E111" t="str">
+        <v/>
+      </c>
+      <c r="F111" t="str">
+        <v>специалист банковских операций</v>
+      </c>
+      <c r="G111" t="str">
+        <v/>
+      </c>
+      <c r="H111" t="str">
+        <v>Специалист банковских операций | Bank Operations | операционист</v>
+      </c>
+      <c r="I111" t="str">
+        <v>банковские операции | платежные транзакции | расчетно кассовое | операционист | back office | бэк офис | депозитарий | кастодиальный</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>Payments</v>
+      </c>
+      <c r="B112" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C112" t="str">
+        <v/>
+      </c>
+      <c r="D112" t="str">
+        <v/>
+      </c>
+      <c r="E112" t="str">
+        <v/>
+      </c>
+      <c r="F112" t="str">
+        <v>менеджер платёжных решений</v>
+      </c>
+      <c r="G112" t="str">
+        <v/>
+      </c>
+      <c r="H112" t="str">
+        <v>Payments Manager | развитие платёжных решений | продукт-менеджер платежей</v>
+      </c>
+      <c r="I112" t="str">
+        <v>платежные решения | платежные системы | payments | эквайринг | развитие платежных решений</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>Dispute</v>
+      </c>
+      <c r="B113" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C113" t="str">
+        <v/>
+      </c>
+      <c r="D113" t="str">
+        <v/>
+      </c>
+      <c r="E113" t="str">
+        <v/>
+      </c>
+      <c r="F113" t="str">
+        <v>диспут-менеджер</v>
+      </c>
+      <c r="G113" t="str">
+        <v/>
+      </c>
+      <c r="H113" t="str">
+        <v>Dispute Manager | Диспут-менеджер | специалист по претензиям</v>
+      </c>
+      <c r="I113" t="str">
+        <v>диспут менеджер | работа с претензиями | чарджбэк | dispute | претензионная работа</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>GR</v>
+      </c>
+      <c r="B114" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C114" t="str">
+        <v>exec</v>
+      </c>
+      <c r="D114" t="str">
+        <v/>
+      </c>
+      <c r="E114" t="str">
+        <v/>
+      </c>
+      <c r="F114" t="str">
+        <v>gr-менеджер</v>
+      </c>
+      <c r="G114" t="str">
+        <v/>
+      </c>
+      <c r="H114" t="str">
+        <v>GR Manager | Government Relations | менеджер по взаимодействию с органами власти</v>
+      </c>
+      <c r="I114" t="str">
+        <v xml:space="preserve"> gr  | government relations | взаимодействие с органами власти | связи с государством | gr менеджер</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>Recruiter</v>
+      </c>
+      <c r="B115" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C115" t="str">
+        <v/>
+      </c>
+      <c r="D115" t="str">
+        <v/>
+      </c>
+      <c r="E115" t="str">
+        <v/>
+      </c>
+      <c r="F115" t="str">
+        <v>рекрутер</v>
+      </c>
+      <c r="G115" t="str">
+        <v/>
+      </c>
+      <c r="H115" t="str">
+        <v>Рекрутер | IT-рекрутер | Talent Acquisition | Sourcer</v>
+      </c>
+      <c r="I115" t="str">
+        <v>рекрутер | recruiter | it рекрутер | talent acquisition | сорсер | sourcer | сорсинг | подбор персонала | рекрутинг | рекрутмент | recruitment</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>HRManager</v>
+      </c>
+      <c r="B116" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C116" t="str">
+        <v/>
+      </c>
+      <c r="D116" t="str">
+        <v/>
+      </c>
+      <c r="E116" t="str">
+        <v/>
+      </c>
+      <c r="F116" t="str">
+        <v>hr-менеджер</v>
+      </c>
+      <c r="G116" t="str">
+        <v/>
+      </c>
+      <c r="H116" t="str">
+        <v>HR-менеджер | HR Generalist | менеджер по персоналу | General HR</v>
+      </c>
+      <c r="I116" t="str">
+        <v>hr менеджер | эйчар | менеджер по персоналу |  hr  | human resources | general hr</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>HRBP</v>
+      </c>
+      <c r="B117" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C117" t="str">
+        <v/>
+      </c>
+      <c r="D117" t="str">
+        <v/>
+      </c>
+      <c r="E117" t="str">
+        <v/>
+      </c>
+      <c r="F117" t="str">
+        <v>hr бизнес-партнёр</v>
+      </c>
+      <c r="G117" t="str">
+        <v/>
+      </c>
+      <c r="H117" t="str">
+        <v>HR Business Partner | HRBP</v>
+      </c>
+      <c r="I117" t="str">
+        <v>hrbp | hr бизнес партнер | hr business partner</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>CnB</v>
+      </c>
+      <c r="B118" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C118" t="str">
+        <v/>
+      </c>
+      <c r="D118" t="str">
+        <v/>
+      </c>
+      <c r="E118" t="str">
+        <v/>
+      </c>
+      <c r="F118" t="str">
+        <v>специалист по компенсациям и льготам</v>
+      </c>
+      <c r="G118" t="str">
+        <v/>
+      </c>
+      <c r="H118" t="str">
+        <v>C&amp;B Specialist | Compensation &amp; Benefits | специалист по C&amp;B</v>
+      </c>
+      <c r="I118" t="str">
+        <v>c&amp;b | компенсации и льготы | compensation | benefits | партнер по компенсациям | sti compensations</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>LnD</v>
+      </c>
+      <c r="B119" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C119" t="str">
+        <v/>
+      </c>
+      <c r="D119" t="str">
+        <v/>
+      </c>
+      <c r="E119" t="str">
+        <v/>
+      </c>
+      <c r="F119" t="str">
+        <v>специалист по обучению и развитию</v>
+      </c>
+      <c r="G119" t="str">
+        <v/>
+      </c>
+      <c r="H119" t="str">
+        <v>L&amp;D Specialist | Learning &amp; Development | тренинг-менеджер</v>
+      </c>
+      <c r="I119" t="str">
+        <v>обучение и развитие | l&amp;d | learning and development | тренинг менеджер | адаптация | автоматизация процессов обучения | t&amp;d | l&amp;d партнер</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>OrgDev</v>
+      </c>
+      <c r="B120" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C120" t="str">
+        <v/>
+      </c>
+      <c r="D120" t="str">
+        <v/>
+      </c>
+      <c r="E120" t="str">
+        <v/>
+      </c>
+      <c r="F120" t="str">
+        <v>специалист по орг. развитию</v>
+      </c>
+      <c r="G120" t="str">
+        <v/>
+      </c>
+      <c r="H120" t="str">
+        <v>Organizational Development | орг. развитие</v>
+      </c>
+      <c r="I120" t="str">
+        <v>организационное развитие | орг развитие | орг. развитие | org development | развитие организации</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>HRAdmin</v>
+      </c>
+      <c r="B121" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C121" t="str">
+        <v/>
+      </c>
+      <c r="D121" t="str">
+        <v/>
+      </c>
+      <c r="E121" t="str">
+        <v/>
+      </c>
+      <c r="F121" t="str">
+        <v>специалист по кадрам</v>
+      </c>
+      <c r="G121" t="str">
+        <v/>
+      </c>
+      <c r="H121" t="str">
+        <v>HR Administrator | Кадровое администрирование | специалист по кадровому делопроизводству</v>
+      </c>
+      <c r="I121" t="str">
+        <v>кадровое администрирование | кадры | кадровое делопроизводство | кадровик | hr администратор | управление кадровым администрированием</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>EmployerBrand</v>
+      </c>
+      <c r="B122" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C122" t="str">
+        <v/>
+      </c>
+      <c r="D122" t="str">
+        <v/>
+      </c>
+      <c r="E122" t="str">
+        <v/>
+      </c>
+      <c r="F122" t="str">
+        <v>менеджер бренда работодателя</v>
+      </c>
+      <c r="G122" t="str">
+        <v/>
+      </c>
+      <c r="H122" t="str">
+        <v>Employer Brand Manager | HR-маркетолог | менеджер бренда работодателя</v>
+      </c>
+      <c r="I122" t="str">
+        <v>бренд работодателя | employer brand | hr бренд | hr маркетинг | hr бренд менеджер</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>InternalComms</v>
+      </c>
+      <c r="B123" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C123" t="str">
+        <v/>
+      </c>
+      <c r="D123" t="str">
+        <v/>
+      </c>
+      <c r="E123" t="str">
+        <v/>
+      </c>
+      <c r="F123" t="str">
+        <v>специалист по внутренним коммуникациям</v>
+      </c>
+      <c r="G123" t="str">
+        <v/>
+      </c>
+      <c r="H123" t="str">
+        <v>Internal Communications | специалист по внутренним коммуникациям</v>
+      </c>
+      <c r="I123" t="str">
+        <v>внутренние коммуникации | внут коммуникации | внут. коммуникации | internal communications | внутриком | внутренний пиар</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>Lawyer</v>
+      </c>
+      <c r="B124" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C124" t="str">
+        <v/>
+      </c>
+      <c r="D124" t="str">
+        <v/>
+      </c>
+      <c r="E124" t="str">
+        <v/>
+      </c>
+      <c r="F124" t="str">
+        <v>юрист</v>
+      </c>
+      <c r="G124" t="str">
+        <v/>
+      </c>
+      <c r="H124" t="str">
+        <v>Юрист | Юрисконсульт | Legal Counsel | Корпоративный юрист</v>
+      </c>
+      <c r="I124" t="str">
+        <v>юрист | юрисконсульт | legal counsel | lawyer | адвокат | корпоративный юрист | правовое сопровождение | правовая поддержка | юриспруденция</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>Procurement</v>
+      </c>
+      <c r="B125" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C125" t="str">
+        <v/>
+      </c>
+      <c r="D125" t="str">
+        <v/>
+      </c>
+      <c r="E125" t="str">
+        <v/>
+      </c>
+      <c r="F125" t="str">
+        <v>специалист по закупкам</v>
+      </c>
+      <c r="G125" t="str">
+        <v/>
+      </c>
+      <c r="H125" t="str">
+        <v>Специалист по закупкам | Procurement Manager | Категорийный менеджер</v>
+      </c>
+      <c r="I125" t="str">
+        <v>закупки | специалист по закупкам | procurement | снабжение | менеджер по закупкам | категорийный менеджер</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>Logistics</v>
+      </c>
+      <c r="B126" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C126" t="str">
+        <v/>
+      </c>
+      <c r="D126" t="str">
+        <v>logist</v>
+      </c>
+      <c r="E126" t="str">
+        <v/>
+      </c>
+      <c r="F126" t="str">
+        <v>логист</v>
+      </c>
+      <c r="G126" t="str">
+        <v/>
+      </c>
+      <c r="H126" t="str">
+        <v>Логист | Менеджер по логистике | Специалист по ВЭД | Supply Chain Manager</v>
+      </c>
+      <c r="I126" t="str">
+        <v>логист | логистика | менеджер по логистике | вэд | специалист по вэд | supply chain | цепочки поставок</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>Warehouse</v>
+      </c>
+      <c r="B127" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C127" t="str">
+        <v/>
+      </c>
+      <c r="D127" t="str">
+        <v>logist</v>
+      </c>
+      <c r="E127" t="str">
+        <v/>
+      </c>
+      <c r="F127" t="str">
+        <v>заведующий складом</v>
+      </c>
+      <c r="G127" t="str">
+        <v/>
+      </c>
+      <c r="H127" t="str">
+        <v>Начальник склада | Заведующий складом | Warehouse Manager</v>
+      </c>
+      <c r="I127" t="str">
+        <v>начальник склада | заведующий складом | warehouse | складская логистика | кладовщик</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>Support</v>
+      </c>
+      <c r="B128" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C128" t="str">
+        <v/>
+      </c>
+      <c r="D128" t="str">
+        <v/>
+      </c>
+      <c r="E128" t="str">
+        <v/>
+      </c>
+      <c r="F128" t="str">
+        <v>специалист поддержки</v>
+      </c>
+      <c r="G128" t="str">
+        <v/>
+      </c>
+      <c r="H128" t="str">
+        <v>Специалист поддержки | Customer Support | Service Desk</v>
+      </c>
+      <c r="I128" t="str">
+        <v>специалист поддержки | customer support | support | техподдержка | служба поддержки | helpdesk | service desk | саппорт | поддержк</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>OfficeManager</v>
+      </c>
+      <c r="B129" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C129" t="str">
+        <v/>
+      </c>
+      <c r="D129" t="str">
+        <v/>
+      </c>
+      <c r="E129" t="str">
+        <v/>
+      </c>
+      <c r="F129" t="str">
+        <v>офис-менеджер</v>
+      </c>
+      <c r="G129" t="str">
+        <v/>
+      </c>
+      <c r="H129" t="str">
+        <v>Офис-менеджер | Office Manager | Административный помощник</v>
+      </c>
+      <c r="I129" t="str">
+        <v>офис менеджер | office manager | администратор офиса | ассистент руководителя | секретарь</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
         <v>GraphicDesigner</v>
       </c>
-      <c r="B92" t="str">
-        <v>nonit</v>
-      </c>
-      <c r="C92" t="str">
-        <v/>
-      </c>
-      <c r="D92" t="str">
+      <c r="B130" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C130" t="str">
+        <v/>
+      </c>
+      <c r="D130" t="str">
         <v>behance | dribbble</v>
       </c>
-      <c r="E92" t="str">
-        <v/>
-      </c>
-      <c r="F92" t="str">
+      <c r="E130" t="str">
+        <v/>
+      </c>
+      <c r="F130" t="str">
         <v>графический дизайнер</v>
       </c>
-      <c r="G92" t="str">
-        <v/>
-      </c>
-      <c r="H92" t="str">
-        <v>Графический дизайнер | Graphic Designer | Motion Designer</v>
-      </c>
-      <c r="I92" t="str">
-        <v>графический дизайнер | graphic designer | моушн дизайнер | motion designer | веб дизайнер | дизайнер</v>
+      <c r="G130" t="str">
+        <v/>
+      </c>
+      <c r="H130" t="str">
+        <v>Графический дизайнер | Graphic Designer | Motion Designer | бренд-дизайнер</v>
+      </c>
+      <c r="I130" t="str">
+        <v>графический дизайнер | graphic designer | графический дизайн | бренд дизайн | брендинг | моушн дизайнер | motion designer | веб дизайнер | дизайнер</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I92"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I130"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/X-Raya-roles.xlsx
+++ b/X-Raya-roles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I130"/>
+  <dimension ref="A1:I131"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -1601,7 +1601,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Cloud</v>
+        <v>DevSecOps</v>
       </c>
       <c r="B42" t="str">
         <v>it</v>
@@ -1613,24 +1613,24 @@
         <v/>
       </c>
       <c r="E42" t="str">
-        <v>cloud engineer</v>
+        <v>devsecops</v>
       </c>
       <c r="F42" t="str">
-        <v>облачный инженер</v>
+        <v>devsecops-инженер</v>
       </c>
       <c r="G42" t="str">
-        <v>Kubernetes</v>
+        <v>Docker | Kubernetes</v>
       </c>
       <c r="H42" t="str">
-        <v>Cloud Engineer | Cloud Architect | инженер облачной инфраструктуры</v>
+        <v>DevSecOps Engineer | Security DevOps | devsecops-инженер</v>
       </c>
       <c r="I42" t="str">
-        <v>cloud engineer | cloud architect | облачный инженер | инженер облачной | aws engineer | azure engineer</v>
+        <v>devsecops | девсекопс | dev sec ops | secops | sec ops | security devops</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Network</v>
+        <v>Cloud</v>
       </c>
       <c r="B43" t="str">
         <v>it</v>
@@ -1642,24 +1642,24 @@
         <v/>
       </c>
       <c r="E43" t="str">
-        <v>network engineer</v>
+        <v>cloud engineer</v>
       </c>
       <c r="F43" t="str">
-        <v>сетевой инженер</v>
+        <v>облачный инженер</v>
       </c>
       <c r="G43" t="str">
-        <v/>
+        <v>Kubernetes</v>
       </c>
       <c r="H43" t="str">
-        <v>Network Engineer | Сетевой инженер | Network Administrator</v>
+        <v>Cloud Engineer | Cloud Architect | инженер облачной инфраструктуры</v>
       </c>
       <c r="I43" t="str">
-        <v>network engineer | сетевой инженер | сетевой администратор | network administrator | инженер сетей</v>
+        <v>cloud engineer | cloud architect | облачный инженер | инженер облачной | aws engineer | azure engineer</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>SysAdmin</v>
+        <v>Network</v>
       </c>
       <c r="B44" t="str">
         <v>it</v>
@@ -1671,24 +1671,24 @@
         <v/>
       </c>
       <c r="E44" t="str">
-        <v>system administrator</v>
+        <v>network engineer</v>
       </c>
       <c r="F44" t="str">
-        <v>системный администратор</v>
+        <v>сетевой инженер</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>System Administrator | Системный администратор | Sysadmin</v>
+        <v>Network Engineer | Сетевой инженер | Network Administrator</v>
       </c>
       <c r="I44" t="str">
-        <v>системный администратор | system administrator | sysadmin | сисадмин | администратор серверов</v>
+        <v>network engineer | сетевой инженер | сетевой администратор | network administrator | инженер сетей</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>WindowsEngineer</v>
+        <v>SysAdmin</v>
       </c>
       <c r="B45" t="str">
         <v>it</v>
@@ -1700,24 +1700,24 @@
         <v/>
       </c>
       <c r="E45" t="str">
-        <v>windows</v>
+        <v>system administrator</v>
       </c>
       <c r="F45" t="str">
-        <v>windows-инженер</v>
+        <v>системный администратор</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Windows Engineer | Windows Administrator | инженер Windows</v>
+        <v>System Administrator | Системный администратор | Sysadmin</v>
       </c>
       <c r="I45" t="str">
-        <v>windows engineer | windows администратор | windows инженер | инженер windows</v>
+        <v>системный администратор | system administrator | sysadmin | сисадмин | администратор серверов</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>StorageEngineer</v>
+        <v>WindowsEngineer</v>
       </c>
       <c r="B46" t="str">
         <v>it</v>
@@ -1729,24 +1729,24 @@
         <v/>
       </c>
       <c r="E46" t="str">
-        <v>storage</v>
+        <v>windows</v>
       </c>
       <c r="F46" t="str">
-        <v>инженер систем хранения</v>
+        <v>windows-инженер</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Storage Engineer | инженер СХД</v>
+        <v>Windows Engineer | Windows Administrator | инженер Windows</v>
       </c>
       <c r="I46" t="str">
-        <v>storage engineer | инженер схд | системы хранения | схд | storage</v>
+        <v>windows engineer | windows администратор | windows инженер | инженер windows</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>DataCenterEngineer</v>
+        <v>StorageEngineer</v>
       </c>
       <c r="B47" t="str">
         <v>it</v>
@@ -1758,24 +1758,24 @@
         <v/>
       </c>
       <c r="E47" t="str">
-        <v>data center</v>
+        <v>storage</v>
       </c>
       <c r="F47" t="str">
-        <v>инженер цод</v>
+        <v>инженер систем хранения</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Data Center Engineer | инженер ЦОД</v>
+        <v>Storage Engineer | инженер СХД</v>
       </c>
       <c r="I47" t="str">
-        <v>data center | инженер цод |  цод  | дата центр | core engineering development</v>
+        <v>storage engineer | инженер схд | системы хранения | схд | storage</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>MDMEngineer</v>
+        <v>DataCenterEngineer</v>
       </c>
       <c r="B48" t="str">
         <v>it</v>
@@ -1787,24 +1787,24 @@
         <v/>
       </c>
       <c r="E48" t="str">
-        <v>master data</v>
+        <v>data center</v>
       </c>
       <c r="F48" t="str">
-        <v>mdm-инженер</v>
+        <v>инженер цод</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>MDM Engineer | Master Data Management</v>
+        <v>Data Center Engineer | инженер ЦОД</v>
       </c>
       <c r="I48" t="str">
-        <v>mdm engineer | master data management | mdm | управление мастер данными</v>
+        <v>data center | инженер цод |  цод  | дата центр | core engineering development</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>DBA</v>
+        <v>MDMEngineer</v>
       </c>
       <c r="B49" t="str">
         <v>it</v>
@@ -1816,24 +1816,24 @@
         <v/>
       </c>
       <c r="E49" t="str">
-        <v>dba</v>
+        <v>master data</v>
       </c>
       <c r="F49" t="str">
-        <v>администратор баз данных</v>
+        <v>mdm-инженер</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Database Administrator | DBA | администратор баз данных</v>
+        <v>MDM Engineer | Master Data Management</v>
       </c>
       <c r="I49" t="str">
-        <v>администратор баз данных | database administrator | database |  dba  | oracle dba | postgres dba | базы данных | база данных</v>
+        <v>mdm engineer | master data management | mdm | управление мастер данными</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>QA</v>
+        <v>DBA</v>
       </c>
       <c r="B50" t="str">
         <v>it</v>
@@ -1845,24 +1845,24 @@
         <v/>
       </c>
       <c r="E50" t="str">
-        <v>qa engineer</v>
+        <v>dba</v>
       </c>
       <c r="F50" t="str">
-        <v>тестировщик</v>
+        <v>администратор баз данных</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>QA Engineer | Test Engineer | тестировщик | инженер по тестированию</v>
+        <v>Database Administrator | DBA | администратор баз данных</v>
       </c>
       <c r="I50" t="str">
-        <v>qa engineer | тестировщик | инженер по тестированию | quality assurance | qa | ручное тестирование | qa manual | qa front | qa load | qa mobile | performance | нагрузочное тестирование</v>
+        <v>администратор баз данных | database administrator | database |  dba  | oracle dba | postgres dba | базы данных | база данных</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>QAAuto</v>
+        <v>QA</v>
       </c>
       <c r="B51" t="str">
         <v>it</v>
@@ -1874,24 +1874,24 @@
         <v/>
       </c>
       <c r="E51" t="str">
-        <v>sdet</v>
+        <v>qa engineer</v>
       </c>
       <c r="F51" t="str">
-        <v>автотестировщик</v>
+        <v>тестировщик</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>QA Automation | SDET | Automation Engineer | автотестировщик</v>
+        <v>QA Engineer | Test Engineer | тестировщик | инженер по тестированию</v>
       </c>
       <c r="I51" t="str">
-        <v>qa automation | automation qa | sdet | автотестировщик | автоматизатор тестирования | автотесты | qa auto</v>
+        <v>qa engineer | тестировщик | инженер по тестированию | quality assurance | qa | ручное тестирование | qa manual | qa front | qa load | qa mobile | performance | нагрузочное тестирование</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Security</v>
+        <v>QAAuto</v>
       </c>
       <c r="B52" t="str">
         <v>it</v>
@@ -1903,24 +1903,24 @@
         <v/>
       </c>
       <c r="E52" t="str">
-        <v>security</v>
+        <v>sdet</v>
       </c>
       <c r="F52" t="str">
-        <v>специалист по информационной безопасности</v>
+        <v>автотестировщик</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Security Engineer | Information Security | AppSec Engineer | специалист по ИБ</v>
+        <v>QA Automation | SDET | Automation Engineer | автотестировщик</v>
       </c>
       <c r="I52" t="str">
-        <v>информационная безопасность | information security | специалист по иб | application security | appsec | security engineer | безопасн | кибербезопасность</v>
+        <v>qa automation | automation qa | sdet | автотестировщик | автоматизатор тестирования | автотесты | qa auto</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Pentester</v>
+        <v>Security</v>
       </c>
       <c r="B53" t="str">
         <v>it</v>
@@ -1932,24 +1932,24 @@
         <v/>
       </c>
       <c r="E53" t="str">
-        <v>penetration</v>
+        <v>security</v>
       </c>
       <c r="F53" t="str">
-        <v>пентестер</v>
+        <v>специалист по информационной безопасности</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Penetration Tester | Ethical Hacker | пентестер</v>
+        <v>Security Engineer | Information Security | AppSec Engineer | специалист по ИБ</v>
       </c>
       <c r="I53" t="str">
-        <v>penetration tester | пентестер | pentest | этичный хакер | red team</v>
+        <v>информационная безопасность | information security | специалист по иб | application security | appsec | security engineer | безопасн | кибербезопасность</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>SystemAnalyst</v>
+        <v>Pentester</v>
       </c>
       <c r="B54" t="str">
         <v>it</v>
@@ -1961,24 +1961,24 @@
         <v/>
       </c>
       <c r="E54" t="str">
-        <v>system analyst</v>
+        <v>penetration</v>
       </c>
       <c r="F54" t="str">
-        <v>системный аналитик</v>
+        <v>пентестер</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Системный аналитик | Systems Analyst</v>
+        <v>Penetration Tester | Ethical Hacker | пентестер</v>
       </c>
       <c r="I54" t="str">
-        <v>системный аналитик | system analyst | systems analyst | системная аналитика</v>
+        <v>penetration tester | пентестер | pentest | этичный хакер | red team</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>BusinessAnalyst</v>
+        <v>SystemAnalyst</v>
       </c>
       <c r="B55" t="str">
         <v>it</v>
@@ -1990,24 +1990,24 @@
         <v/>
       </c>
       <c r="E55" t="str">
-        <v>business analyst</v>
+        <v>system analyst</v>
       </c>
       <c r="F55" t="str">
-        <v>бизнес-аналитик</v>
+        <v>системный аналитик</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Бизнес-аналитик | Business Analyst</v>
+        <v>Системный аналитик | Systems Analyst</v>
       </c>
       <c r="I55" t="str">
-        <v>бизнес аналитик | business analyst | бизнес анализ | bpm аналитик</v>
+        <v>системный аналитик | system analyst | systems analyst | системная аналитика</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Analyst</v>
+        <v>BusinessAnalyst</v>
       </c>
       <c r="B56" t="str">
         <v>it</v>
@@ -2019,24 +2019,24 @@
         <v/>
       </c>
       <c r="E56" t="str">
-        <v>analyst</v>
+        <v>business analyst</v>
       </c>
       <c r="F56" t="str">
-        <v>аналитик</v>
+        <v>бизнес-аналитик</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Аналитик | Analyst</v>
+        <v>Бизнес-аналитик | Business Analyst</v>
       </c>
       <c r="I56" t="str">
-        <v>аналитик | analyst</v>
+        <v>бизнес аналитик | business analyst | бизнес анализ | bpm аналитик</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ProductAnalyst</v>
+        <v>Analyst</v>
       </c>
       <c r="B57" t="str">
         <v>it</v>
@@ -2048,24 +2048,24 @@
         <v/>
       </c>
       <c r="E57" t="str">
-        <v>product analyst</v>
+        <v>analyst</v>
       </c>
       <c r="F57" t="str">
-        <v>продуктовый аналитик</v>
+        <v>аналитик</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Продуктовый аналитик | Product Analyst</v>
+        <v>Аналитик | Analyst</v>
       </c>
       <c r="I57" t="str">
-        <v>продуктовый аналитик | product analyst | продуктовая аналитика</v>
+        <v>аналитик | analyst</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>WebAnalyst</v>
+        <v>ProductAnalyst</v>
       </c>
       <c r="B58" t="str">
         <v>it</v>
@@ -2077,24 +2077,24 @@
         <v/>
       </c>
       <c r="E58" t="str">
-        <v>web analyst</v>
+        <v>product analyst</v>
       </c>
       <c r="F58" t="str">
-        <v>веб-аналитик</v>
+        <v>продуктовый аналитик</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Web Analyst | веб-аналитик | аналитик веб-аналитики</v>
+        <v>Продуктовый аналитик | Product Analyst</v>
       </c>
       <c r="I58" t="str">
-        <v>web analyst | веб аналитик | web аналитик | веб аналитика</v>
+        <v>продуктовый аналитик | product analyst | продуктовая аналитика</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>PM</v>
+        <v>WebAnalyst</v>
       </c>
       <c r="B59" t="str">
         <v>it</v>
@@ -2106,24 +2106,24 @@
         <v/>
       </c>
       <c r="E59" t="str">
-        <v>product manager</v>
+        <v>web analyst</v>
       </c>
       <c r="F59" t="str">
-        <v>менеджер продукта</v>
+        <v>веб-аналитик</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Product Manager | Product Owner | продакт менеджер | продакт</v>
+        <v>Web Analyst | веб-аналитик | аналитик веб-аналитики</v>
       </c>
       <c r="I59" t="str">
-        <v>product manager | продакт менеджер | продакт | product owner | продакт оунер | менеджер продукта | technical product manager | ml product manager</v>
+        <v>web analyst | веб аналитик | web аналитик | веб аналитика</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ProjectManager</v>
+        <v>PM</v>
       </c>
       <c r="B60" t="str">
         <v>it</v>
@@ -2135,24 +2135,24 @@
         <v/>
       </c>
       <c r="E60" t="str">
-        <v>project manager</v>
+        <v>product manager</v>
       </c>
       <c r="F60" t="str">
-        <v>проджект-менеджер</v>
+        <v>менеджер продукта</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Project Manager | проджект менеджер | руководитель проекта</v>
+        <v>Product Manager | Product Owner | продакт менеджер | продакт</v>
       </c>
       <c r="I60" t="str">
-        <v>project manager | проджект менеджер | проджект | руководитель проекта | управление проектами | it project manager</v>
+        <v>product manager | продакт менеджер | продакт | product owner | продакт оунер | менеджер продукта | technical product manager | ml product manager</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ReleaseManager</v>
+        <v>ProjectManager</v>
       </c>
       <c r="B61" t="str">
         <v>it</v>
@@ -2164,24 +2164,24 @@
         <v/>
       </c>
       <c r="E61" t="str">
-        <v>release manager</v>
+        <v>project manager</v>
       </c>
       <c r="F61" t="str">
-        <v>релиз-менеджер</v>
+        <v>проджект-менеджер</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Release Manager | менеджер выпуска | релиз-менеджер</v>
+        <v>Project Manager | проджект менеджер | руководитель проекта</v>
       </c>
       <c r="I61" t="str">
-        <v>release manager | менеджер выпуска | релиз менеджер | управление релизами</v>
+        <v>project manager | проджект менеджер | проджект | руководитель проекта | управление проектами | it project manager</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ScrumMaster</v>
+        <v>ReleaseManager</v>
       </c>
       <c r="B62" t="str">
         <v>it</v>
@@ -2193,24 +2193,24 @@
         <v/>
       </c>
       <c r="E62" t="str">
-        <v>scrum master</v>
+        <v>release manager</v>
       </c>
       <c r="F62" t="str">
-        <v>скрам-мастер</v>
+        <v>релиз-менеджер</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Scrum Master | Agile Coach | скрам-мастер</v>
+        <v>Release Manager | менеджер выпуска | релиз-менеджер</v>
       </c>
       <c r="I62" t="str">
-        <v>scrum master | скрам мастер | agile coach | аджайл коуч</v>
+        <v>release manager | менеджер выпуска | релиз менеджер | управление релизами</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Architect</v>
+        <v>ScrumMaster</v>
       </c>
       <c r="B63" t="str">
         <v>it</v>
@@ -2222,24 +2222,24 @@
         <v/>
       </c>
       <c r="E63" t="str">
-        <v>architect</v>
+        <v>scrum master</v>
       </c>
       <c r="F63" t="str">
-        <v>архитектор</v>
+        <v>скрам-мастер</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Solution Architect | Software Architect | System Architect | Архитектор ПО</v>
+        <v>Scrum Master | Agile Coach | скрам-мастер</v>
       </c>
       <c r="I63" t="str">
-        <v>solution architect | software architect | system architect | системный архитектор | архитектор по | архитектор решений | архитектор телеком</v>
+        <v>scrum master | скрам мастер | agile coach | аджайл коуч</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>TechWriter</v>
+        <v>Architect</v>
       </c>
       <c r="B64" t="str">
         <v>it</v>
@@ -2251,24 +2251,24 @@
         <v/>
       </c>
       <c r="E64" t="str">
-        <v>technical writer</v>
+        <v>architect</v>
       </c>
       <c r="F64" t="str">
-        <v>технический писатель</v>
+        <v>архитектор</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Technical Writer | технический писатель | документатор</v>
+        <v>Solution Architect | Software Architect | System Architect | Архитектор ПО</v>
       </c>
       <c r="I64" t="str">
-        <v>technical writer | технический писатель | техписатель | documentation engineer</v>
+        <v>solution architect | software architect | system architect | системный архитектор | архитектор по | архитектор решений | архитектор телеком</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>DevRel</v>
+        <v>TechWriter</v>
       </c>
       <c r="B65" t="str">
         <v>it</v>
@@ -2280,24 +2280,24 @@
         <v/>
       </c>
       <c r="E65" t="str">
-        <v>developer advocate</v>
+        <v>technical writer</v>
       </c>
       <c r="F65" t="str">
-        <v>devrel</v>
+        <v>технический писатель</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Developer Advocate | Developer Relations | DevRel</v>
+        <v>Technical Writer | технический писатель | документатор</v>
       </c>
       <c r="I65" t="str">
-        <v>developer advocate | developer relations | devrel | деврел</v>
+        <v>technical writer | технический писатель | техписатель | documentation engineer</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>SupportEngineer</v>
+        <v>DevRel</v>
       </c>
       <c r="B66" t="str">
         <v>it</v>
@@ -2309,24 +2309,24 @@
         <v/>
       </c>
       <c r="E66" t="str">
-        <v>support engineer</v>
+        <v>developer advocate</v>
       </c>
       <c r="F66" t="str">
-        <v>инженер поддержки</v>
+        <v>devrel</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Support Engineer | Technical Support Engineer | 2nd/3rd Line Support</v>
+        <v>Developer Advocate | Developer Relations | DevRel</v>
       </c>
       <c r="I66" t="str">
-        <v>support engineer | инженер поддержки | инженер технической поддержки | l2 support | l3 support | 2nd line | 3rd line | вторая линия | третья линия | тех сопровождение | техническое сопровождение | сопровождени</v>
+        <v>developer advocate | developer relations | devrel | деврел</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>GovTech</v>
+        <v>SupportEngineer</v>
       </c>
       <c r="B67" t="str">
         <v>it</v>
@@ -2338,24 +2338,24 @@
         <v/>
       </c>
       <c r="E67" t="str">
-        <v>govtech</v>
+        <v>support engineer</v>
       </c>
       <c r="F67" t="str">
-        <v>цифровые госсервисы</v>
+        <v>инженер поддержки</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>GovTech | Цифровые государственные сервисы | гос.технологии</v>
+        <v>Support Engineer | Technical Support Engineer | 2nd/3rd Line Support</v>
       </c>
       <c r="I67" t="str">
-        <v>govtech | цифровые государственные сервисы | гос технологии | гос.технологии | гостех | госсервисы | государственные сервисы</v>
+        <v>support engineer | инженер поддержки | инженер технической поддержки | l2 support | l3 support | 2nd line | 3rd line | вторая линия | третья линия | тех сопровождение | техническое сопровождение | сопровождени</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>ProductDesigner</v>
+        <v>GovTech</v>
       </c>
       <c r="B68" t="str">
         <v>it</v>
@@ -2364,27 +2364,27 @@
         <v/>
       </c>
       <c r="D68" t="str">
-        <v>behance | dribbble | dprofile</v>
+        <v/>
       </c>
       <c r="E68" t="str">
-        <v/>
+        <v>govtech</v>
       </c>
       <c r="F68" t="str">
-        <v>продуктовый дизайнер</v>
+        <v>цифровые госсервисы</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Product Designer | UX/UI Designer | UX Designer | UI Designer | продуктовый дизайнер</v>
+        <v>GovTech | Цифровые государственные сервисы | гос.технологии</v>
       </c>
       <c r="I68" t="str">
-        <v>product designer | продуктовый дизайнер | продуктовый дизайн | ux designer | ui designer | ux ui | ux дизайнер | ui дизайнер | дизайнер интерфейсов</v>
+        <v>govtech | цифровые государственные сервисы | гос технологии | гос.технологии | гостех | госсервисы | государственные сервисы</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>UXResearcher</v>
+        <v>ProductDesigner</v>
       </c>
       <c r="B69" t="str">
         <v>it</v>
@@ -2393,56 +2393,56 @@
         <v/>
       </c>
       <c r="D69" t="str">
-        <v>dprofile</v>
+        <v>behance | dribbble | dprofile</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>ux-исследователь</v>
+        <v>продуктовый дизайнер</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>UX Researcher | User Researcher | ux-исследователь</v>
+        <v>Product Designer | UX/UI Designer | UX Designer | UI Designer | продуктовый дизайнер</v>
       </c>
       <c r="I69" t="str">
-        <v>ux researcher | ux исследователь | user researcher | юзабилити | исследования интерфейсов</v>
+        <v>product designer | продуктовый дизайнер | продуктовый дизайн | ux designer | ui designer | ux ui | ux дизайнер | ui дизайнер | дизайнер интерфейсов</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>CEO</v>
+        <v>UXResearcher</v>
       </c>
       <c r="B70" t="str">
-        <v>nonit</v>
+        <v>it</v>
       </c>
       <c r="C70" t="str">
-        <v>exec</v>
+        <v/>
       </c>
       <c r="D70" t="str">
-        <v/>
+        <v>dprofile</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>генеральный директор</v>
+        <v>ux-исследователь</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>CEO | Chief Executive Officer | генеральный директор | Managing Director</v>
+        <v>UX Researcher | User Researcher | ux-исследователь</v>
       </c>
       <c r="I70" t="str">
-        <v>ceo | chief executive officer | генеральный директор | гендиректор | управляющий директор</v>
+        <v>ux researcher | ux исследователь | user researcher | юзабилити | исследования интерфейсов</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>CFO</v>
+        <v>CEO</v>
       </c>
       <c r="B71" t="str">
         <v>nonit</v>
@@ -2457,21 +2457,21 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>финансовый директор</v>
+        <v>генеральный директор</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>CFO | Chief Financial Officer | финансовый директор</v>
+        <v>CEO | Chief Executive Officer | генеральный директор | Managing Director</v>
       </c>
       <c r="I71" t="str">
-        <v>cfo | chief financial officer | финансовый директор | фин директор</v>
+        <v>ceo | chief executive officer | генеральный директор | гендиректор | управляющий директор</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>COO</v>
+        <v>CFO</v>
       </c>
       <c r="B72" t="str">
         <v>nonit</v>
@@ -2486,21 +2486,21 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>операционный директор</v>
+        <v>финансовый директор</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>COO | Chief Operating Officer | операционный директор</v>
+        <v>CFO | Chief Financial Officer | финансовый директор</v>
       </c>
       <c r="I72" t="str">
-        <v>coo | chief operating officer | операционный директор</v>
+        <v>cfo | chief financial officer | финансовый директор | фин директор</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>CMO</v>
+        <v>COO</v>
       </c>
       <c r="B73" t="str">
         <v>nonit</v>
@@ -2515,21 +2515,21 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>директор по маркетингу</v>
+        <v>операционный директор</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>CMO | Chief Marketing Officer | директор по маркетингу</v>
+        <v>COO | Chief Operating Officer | операционный директор</v>
       </c>
       <c r="I73" t="str">
-        <v>cmo | chief marketing officer | директор по маркетингу | маркетинг директор</v>
+        <v>coo | chief operating officer | операционный директор</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>HRD</v>
+        <v>CMO</v>
       </c>
       <c r="B74" t="str">
         <v>nonit</v>
@@ -2544,21 +2544,21 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>директор по персоналу</v>
+        <v>директор по маркетингу</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>HRD | CHRO | HR Director | директор по персоналу</v>
+        <v>CMO | Chief Marketing Officer | директор по маркетингу</v>
       </c>
       <c r="I74" t="str">
-        <v>chro | hrd | hr director | директор по персоналу | hr директор</v>
+        <v>cmo | chief marketing officer | директор по маркетингу | маркетинг директор</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Commercial</v>
+        <v>HRD</v>
       </c>
       <c r="B75" t="str">
         <v>nonit</v>
@@ -2573,21 +2573,21 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>коммерческий директор</v>
+        <v>директор по персоналу</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Коммерческий директор | Commercial Director | CCO</v>
+        <v>HRD | CHRO | HR Director | директор по персоналу</v>
       </c>
       <c r="I75" t="str">
-        <v>коммерческий директор | commercial director | cco | директор по продажам</v>
+        <v>chro | hrd | hr director | директор по персоналу | hr директор</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Management</v>
+        <v>Commercial</v>
       </c>
       <c r="B76" t="str">
         <v>nonit</v>
@@ -2602,27 +2602,27 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>руководитель</v>
+        <v>коммерческий директор</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>General Manager | Руководитель | Директор | управляющий</v>
+        <v>Коммерческий директор | Commercial Director | CCO</v>
       </c>
       <c r="I76" t="str">
-        <v>general manager | управление | управляющий | общекорпоративное развитие | руководитель направления | руководитель подразделения</v>
+        <v>коммерческий директор | commercial director | cco | директор по продажам</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Marketing</v>
+        <v>Management</v>
       </c>
       <c r="B77" t="str">
         <v>nonit</v>
       </c>
       <c r="C77" t="str">
-        <v/>
+        <v>exec</v>
       </c>
       <c r="D77" t="str">
         <v/>
@@ -2631,21 +2631,21 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>маркетолог</v>
+        <v>руководитель</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Маркетолог | Интернет-маркетолог | Digital Marketing</v>
+        <v>General Manager | Руководитель | Директор | управляющий</v>
       </c>
       <c r="I77" t="str">
-        <v>маркетолог | интернет маркетолог | digital marketing | диджитал маркетолог | маркетинг | маркетинговые коммуникации | онлайн привлечение | маркетинговый аналитик</v>
+        <v>general manager | управление | управляющий | общекорпоративное развитие | руководитель направления | руководитель подразделения</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>SMM</v>
+        <v>Marketing</v>
       </c>
       <c r="B78" t="str">
         <v>nonit</v>
@@ -2660,21 +2660,21 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>smm-менеджер</v>
+        <v>маркетолог</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>SMM-менеджер | Social Media Manager | контент-мейкер</v>
+        <v>Маркетолог | Интернет-маркетолог | Digital Marketing</v>
       </c>
       <c r="I78" t="str">
-        <v>smm | smm менеджер | social media | сммщик</v>
+        <v>маркетолог | интернет маркетолог | digital marketing | диджитал маркетолог | маркетинг | маркетинговые коммуникации | онлайн привлечение | маркетинговый аналитик</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Targetolog</v>
+        <v>SMM</v>
       </c>
       <c r="B79" t="str">
         <v>nonit</v>
@@ -2689,21 +2689,21 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>таргетолог</v>
+        <v>smm-менеджер</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Таргетолог | Targeting Specialist | специалист по таргетированной рекламе</v>
+        <v>SMM-менеджер | Social Media Manager | контент-мейкер</v>
       </c>
       <c r="I79" t="str">
-        <v>таргетолог | таргетированная реклама | таргет | target</v>
+        <v>smm | smm менеджер | social media | сммщик</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>SEO</v>
+        <v>Targetolog</v>
       </c>
       <c r="B80" t="str">
         <v>nonit</v>
@@ -2718,21 +2718,21 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>seo-специалист</v>
+        <v>таргетолог</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>SEO-специалист | SEO Specialist | поисковый оптимизатор</v>
+        <v>Таргетолог | Targeting Specialist | специалист по таргетированной рекламе</v>
       </c>
       <c r="I80" t="str">
-        <v>seo | seo специалист | сео | поисковая оптимизация | поисковое продвижение | сеошник</v>
+        <v>таргетолог | таргетированная реклама | таргет | target</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>PPC</v>
+        <v>SEO</v>
       </c>
       <c r="B81" t="str">
         <v>nonit</v>
@@ -2747,21 +2747,21 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>специалист по контекстной рекламе</v>
+        <v>seo-специалист</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>PPC Specialist | Специалист по контекстной рекламе | Директолог</v>
+        <v>SEO-специалист | SEO Specialist | поисковый оптимизатор</v>
       </c>
       <c r="I81" t="str">
-        <v>ppc | контекстная реклама | контекстная и медийная реклама | медийная реклама | контекстолог | директолог | специалист по рекламе | performance marketing | перформанс</v>
+        <v>seo | seo специалист | сео | поисковая оптимизация | поисковое продвижение | сеошник</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Influence</v>
+        <v>PPC</v>
       </c>
       <c r="B82" t="str">
         <v>nonit</v>
@@ -2776,21 +2776,21 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>менеджер по работе с блогерами</v>
+        <v>специалист по контекстной рекламе</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Influencer Marketing Manager | Менеджер по работе с блогерами</v>
+        <v>PPC Specialist | Специалист по контекстной рекламе | Директолог</v>
       </c>
       <c r="I82" t="str">
-        <v>работа с блогерами | инфлюенс | influencer marketing | блогеры | инфлюенсер</v>
+        <v>ppc | контекстная реклама | контекстная и медийная реклама | медийная реклама | контекстолог | директолог | специалист по рекламе | performance marketing | перформанс</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>PR</v>
+        <v>Influence</v>
       </c>
       <c r="B83" t="str">
         <v>nonit</v>
@@ -2805,21 +2805,21 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>pr-менеджер</v>
+        <v>менеджер по работе с блогерами</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>PR-менеджер | PR Manager | Public Relations</v>
+        <v>Influencer Marketing Manager | Менеджер по работе с блогерами</v>
       </c>
       <c r="I83" t="str">
-        <v>pr менеджер |  pr  | пиар | public relations | связям с общественностью | связи с общественностью | pr manager</v>
+        <v>работа с блогерами | инфлюенс | influencer marketing | блогеры | инфлюенсер</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>SERM</v>
+        <v>PR</v>
       </c>
       <c r="B84" t="str">
         <v>nonit</v>
@@ -2834,21 +2834,21 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>специалист по репутации</v>
+        <v>pr-менеджер</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>SERM Specialist | Репутационный маркетинг | ORM</v>
+        <v>PR-менеджер | PR Manager | Public Relations</v>
       </c>
       <c r="I84" t="str">
-        <v>serm | репутационный маркетинг | orm | управление репутацией</v>
+        <v>pr менеджер |  pr  | пиар | public relations | связям с общественностью | связи с общественностью | pr manager</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>BrandManager</v>
+        <v>SERM</v>
       </c>
       <c r="B85" t="str">
         <v>nonit</v>
@@ -2863,21 +2863,21 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>бренд-менеджер</v>
+        <v>специалист по репутации</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Бренд-менеджер | Brand Manager</v>
+        <v>SERM Specialist | Репутационный маркетинг | ORM</v>
       </c>
       <c r="I85" t="str">
-        <v>бренд менеджер | brand manager | управление брендом</v>
+        <v>serm | репутационный маркетинг | orm | управление репутацией</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Event</v>
+        <v>BrandManager</v>
       </c>
       <c r="B86" t="str">
         <v>nonit</v>
@@ -2892,21 +2892,21 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>event-менеджер</v>
+        <v>бренд-менеджер</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Event Manager | Ивент-менеджер | организатор мероприятий</v>
+        <v>Бренд-менеджер | Brand Manager</v>
       </c>
       <c r="I86" t="str">
-        <v>event manager | ивент | ивент маркетинг | event маркетинг | организатор мероприятий</v>
+        <v>бренд менеджер | brand manager | управление брендом</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Content</v>
+        <v>Event</v>
       </c>
       <c r="B87" t="str">
         <v>nonit</v>
@@ -2921,21 +2921,21 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>копирайтер</v>
+        <v>event-менеджер</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Копирайтер | Контент-менеджер | Редактор | Технический писатель</v>
+        <v>Event Manager | Ивент-менеджер | организатор мероприятий</v>
       </c>
       <c r="I87" t="str">
-        <v>копирайтер | copywriter | контент менеджер | content manager | редактор | редактура | автор текстов | контент | ux редактор | линейный редактор</v>
+        <v>event manager | ивент | ивент маркетинг | event маркетинг | организатор мероприятий</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Producer</v>
+        <v>Content</v>
       </c>
       <c r="B88" t="str">
         <v>nonit</v>
@@ -2950,21 +2950,21 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>продюсер</v>
+        <v>копирайтер</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Продюсер | Producer | Видеопродюсер</v>
+        <v>Копирайтер | Контент-менеджер | Редактор | Технический писатель</v>
       </c>
       <c r="I88" t="str">
-        <v>продюсер | producer | видеопродюсер | контент продюсер</v>
+        <v>копирайтер | copywriter | контент менеджер | content manager | редактор | редактура | автор текстов | контент | ux редактор | линейный редактор</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Director</v>
+        <v>Producer</v>
       </c>
       <c r="B89" t="str">
         <v>nonit</v>
@@ -2979,21 +2979,21 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>режиссёр</v>
+        <v>продюсер</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Режиссёр | Director | Режиссёр монтажа</v>
+        <v>Продюсер | Producer | Видеопродюсер</v>
       </c>
       <c r="I89" t="str">
-        <v>режиссер | режиссёр | director | режиссер монтажа</v>
+        <v>продюсер | producer | видеопродюсер | контент продюсер</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>VideoStudio</v>
+        <v>Director</v>
       </c>
       <c r="B90" t="str">
         <v>nonit</v>
@@ -3008,21 +3008,21 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>видеограф</v>
+        <v>режиссёр</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Видеограф | Video Editor | специалист видеостудии</v>
+        <v>Режиссёр | Director | Режиссёр монтажа</v>
       </c>
       <c r="I90" t="str">
-        <v>видеограф | видеомонтаж | видеостуди | видеооператор | video editor | монтажер</v>
+        <v>режиссер | режиссёр | director | режиссер монтажа</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>MediaManager</v>
+        <v>VideoStudio</v>
       </c>
       <c r="B91" t="str">
         <v>nonit</v>
@@ -3037,21 +3037,21 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>менеджер по медиа</v>
+        <v>видеограф</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Media Manager | Медиабаер | менеджер по работе с медиа</v>
+        <v>Видеограф | Video Editor | специалист видеостудии</v>
       </c>
       <c r="I91" t="str">
-        <v>управление медиа | медиабаинг | медиабаер | работа с медиа | медиаменеджер | media buying</v>
+        <v>видеограф | видеомонтаж | видеостуди | видеооператор | video editor | монтажер</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Distribution</v>
+        <v>MediaManager</v>
       </c>
       <c r="B92" t="str">
         <v>nonit</v>
@@ -3066,21 +3066,21 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>менеджер по дистрибуции</v>
+        <v>менеджер по медиа</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Distribution Manager | менеджер по дистрибуции</v>
+        <v>Media Manager | Медиабаер | менеджер по работе с медиа</v>
       </c>
       <c r="I92" t="str">
-        <v>дистрибуция | distribution | дистрибьютор | менеджер по дистрибуции</v>
+        <v>управление медиа | медиабаинг | медиабаер | работа с медиа | медиаменеджер | media buying</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Localization</v>
+        <v>Distribution</v>
       </c>
       <c r="B93" t="str">
         <v>nonit</v>
@@ -3095,21 +3095,21 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>специалист по локализации</v>
+        <v>менеджер по дистрибуции</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Localization Specialist | Переводчик | менеджер локализации</v>
+        <v>Distribution Manager | менеджер по дистрибуции</v>
       </c>
       <c r="I93" t="str">
-        <v>локализация | localization | переводчик | локализатор</v>
+        <v>дистрибуция | distribution | дистрибьютор | менеджер по дистрибуции</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>CXResearch</v>
+        <v>Localization</v>
       </c>
       <c r="B94" t="str">
         <v>nonit</v>
@@ -3124,27 +3124,27 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>исследователь клиентского опыта</v>
+        <v>специалист по локализации</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>CX Researcher | Customer Experience Researcher | аналитик CX</v>
+        <v>Localization Specialist | Переводчик | менеджер локализации</v>
       </c>
       <c r="I94" t="str">
-        <v>cx исследования | customer experience | аналитик cx | клиентский опыт | cx research | cx аналитик</v>
+        <v>локализация | localization | переводчик | локализатор</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Sales</v>
+        <v>CXResearch</v>
       </c>
       <c r="B95" t="str">
         <v>nonit</v>
       </c>
       <c r="C95" t="str">
-        <v>exec</v>
+        <v/>
       </c>
       <c r="D95" t="str">
         <v/>
@@ -3153,21 +3153,21 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>менеджер по продажам</v>
+        <v>исследователь клиентского опыта</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Менеджер по продажам | Sales Manager | Account Manager | Руководитель отдела продаж</v>
+        <v>CX Researcher | Customer Experience Researcher | аналитик CX</v>
       </c>
       <c r="I95" t="str">
-        <v>менеджер по продажам | sales manager | account manager | аккаунт менеджер | руководитель отдела продаж | роп | продажи | развитие продаж</v>
+        <v>cx исследования | customer experience | аналитик cx | клиентский опыт | cx research | cx аналитик</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>KAM</v>
+        <v>Sales</v>
       </c>
       <c r="B96" t="str">
         <v>nonit</v>
@@ -3182,21 +3182,21 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>менеджер по работе с ключевыми клиентами</v>
+        <v>менеджер по продажам</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Key Account Manager | KAM | менеджер по ключевым клиентам</v>
+        <v>Менеджер по продажам | Sales Manager | Account Manager | Руководитель отдела продаж</v>
       </c>
       <c r="I96" t="str">
-        <v>key account | kam | ключевые клиенты | менеджер по ключевым клиентам</v>
+        <v>менеджер по продажам | sales manager | account manager | аккаунт менеджер | руководитель отдела продаж | роп | продажи | развитие продаж</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>BizDev</v>
+        <v>KAM</v>
       </c>
       <c r="B97" t="str">
         <v>nonit</v>
@@ -3211,27 +3211,27 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>менеджер по развитию бизнеса</v>
+        <v>менеджер по работе с ключевыми клиентами</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Business Development Manager | BizDev | развитие бизнеса</v>
+        <v>Key Account Manager | KAM | менеджер по ключевым клиентам</v>
       </c>
       <c r="I97" t="str">
-        <v>business development | bizdev | биздев | развитие бизнеса | менеджер по развитию</v>
+        <v>key account | kam | ключевые клиенты | менеджер по ключевым клиентам</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>CustomerSuccess</v>
+        <v>BizDev</v>
       </c>
       <c r="B98" t="str">
         <v>nonit</v>
       </c>
       <c r="C98" t="str">
-        <v/>
+        <v>exec</v>
       </c>
       <c r="D98" t="str">
         <v/>
@@ -3240,21 +3240,21 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>менеджер по работе с клиентами</v>
+        <v>менеджер по развитию бизнеса</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Customer Success Manager | Account Manager | менеджер по клиентам</v>
+        <v>Business Development Manager | BizDev | развитие бизнеса</v>
       </c>
       <c r="I98" t="str">
-        <v>customer success | csm | менеджер по работе с клиентами | клиентский сервис | управление клиентским сервисом | развитие сервиса</v>
+        <v>business development | bizdev | биздев | развитие бизнеса | менеджер по развитию</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Accountant</v>
+        <v>CustomerSuccess</v>
       </c>
       <c r="B99" t="str">
         <v>nonit</v>
@@ -3269,21 +3269,21 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>бухгалтер</v>
+        <v>менеджер по работе с клиентами</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Бухгалтер | Главный бухгалтер | Accountant</v>
+        <v>Customer Success Manager | Account Manager | менеджер по клиентам</v>
       </c>
       <c r="I99" t="str">
-        <v>бухгалтер | accountant | главный бухгалтер | главбух | бухгалтерия</v>
+        <v>customer success | csm | менеджер по работе с клиентами | клиентский сервис | управление клиентским сервисом | развитие сервиса</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>FinAnalyst</v>
+        <v>Accountant</v>
       </c>
       <c r="B100" t="str">
         <v>nonit</v>
@@ -3298,21 +3298,21 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>финансовый аналитик</v>
+        <v>бухгалтер</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Финансовый аналитик | Financial Analyst | финансовый аналитик данных</v>
+        <v>Бухгалтер | Главный бухгалтер | Accountant</v>
       </c>
       <c r="I100" t="str">
-        <v>финансовый аналитик | financial analyst | финансовая аналитика | финансовый аналитик данных</v>
+        <v>бухгалтер | accountant | главный бухгалтер | главбух | бухгалтерия</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Finance</v>
+        <v>FinAnalyst</v>
       </c>
       <c r="B101" t="str">
         <v>nonit</v>
@@ -3327,21 +3327,21 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>финансовый менеджер</v>
+        <v>финансовый аналитик</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Финансовый менеджер | Finance Manager | Финансовый бизнес-партнёр</v>
+        <v>Финансовый аналитик | Financial Analyst | финансовый аналитик данных</v>
       </c>
       <c r="I101" t="str">
-        <v>финансы | финансовый менеджер | финансовый бизнес партнер | finance | финансист | корпоративное финансирование</v>
+        <v>финансовый аналитик | financial analyst | финансовая аналитика | финансовый аналитик данных</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Auditor</v>
+        <v>Finance</v>
       </c>
       <c r="B102" t="str">
         <v>nonit</v>
@@ -3356,21 +3356,21 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>аудитор</v>
+        <v>финансовый менеджер</v>
       </c>
       <c r="G102" t="str">
         <v/>
       </c>
       <c r="H102" t="str">
-        <v>Аудитор | Auditor | внутренний аудит</v>
+        <v>Финансовый менеджер | Finance Manager | Финансовый бизнес-партнёр</v>
       </c>
       <c r="I102" t="str">
-        <v>аудитор | auditor | аудит | внутренний аудит | ит аудит</v>
+        <v>финансы | финансовый менеджер | финансовый бизнес партнер | finance | финансист | корпоративное финансирование</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Economist</v>
+        <v>Auditor</v>
       </c>
       <c r="B103" t="str">
         <v>nonit</v>
@@ -3385,21 +3385,21 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>экономист</v>
+        <v>аудитор</v>
       </c>
       <c r="G103" t="str">
         <v/>
       </c>
       <c r="H103" t="str">
-        <v>Экономист | Economist | планово-экономический</v>
+        <v>Аудитор | Auditor | внутренний аудит</v>
       </c>
       <c r="I103" t="str">
-        <v>экономист | economist | планирование бюджета</v>
+        <v>аудитор | auditor | аудит | внутренний аудит | ит аудит</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Tax</v>
+        <v>Economist</v>
       </c>
       <c r="B104" t="str">
         <v>nonit</v>
@@ -3414,21 +3414,21 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>налоговый специалист</v>
+        <v>экономист</v>
       </c>
       <c r="G104" t="str">
         <v/>
       </c>
       <c r="H104" t="str">
-        <v>Налоговый менеджер | Tax Manager | налоговый консультант</v>
+        <v>Экономист | Economist | планово-экономический</v>
       </c>
       <c r="I104" t="str">
-        <v>налоги | налоговый | tax | налогообложение | налоговый консультант</v>
+        <v>экономист | economist | планирование бюджета</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Treasury</v>
+        <v>Tax</v>
       </c>
       <c r="B105" t="str">
         <v>nonit</v>
@@ -3443,21 +3443,21 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>казначей</v>
+        <v>налоговый специалист</v>
       </c>
       <c r="G105" t="str">
         <v/>
       </c>
       <c r="H105" t="str">
-        <v>Казначей | Treasury Manager | специалист казначейства</v>
+        <v>Налоговый менеджер | Tax Manager | налоговый консультант</v>
       </c>
       <c r="I105" t="str">
-        <v>казначейство | казначей | treasury | технология расчетов</v>
+        <v>налоги | налоговый | tax | налогообложение | налоговый консультант</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Actuary</v>
+        <v>Treasury</v>
       </c>
       <c r="B106" t="str">
         <v>nonit</v>
@@ -3472,27 +3472,27 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>актуарий</v>
+        <v>казначей</v>
       </c>
       <c r="G106" t="str">
         <v/>
       </c>
       <c r="H106" t="str">
-        <v>Актуарий | Actuary</v>
+        <v>Казначей | Treasury Manager | специалист казначейства</v>
       </c>
       <c r="I106" t="str">
-        <v>актуарий | actuary | актуарии | актуарные расчеты</v>
+        <v>казначейство | казначей | treasury | технология расчетов</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Investment</v>
+        <v>Actuary</v>
       </c>
       <c r="B107" t="str">
         <v>nonit</v>
       </c>
       <c r="C107" t="str">
-        <v>exec</v>
+        <v/>
       </c>
       <c r="D107" t="str">
         <v/>
@@ -3501,27 +3501,27 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>инвестиционный менеджер</v>
+        <v>актуарий</v>
       </c>
       <c r="G107" t="str">
         <v/>
       </c>
       <c r="H107" t="str">
-        <v>Investment Manager | Инвестиционный аналитик | инвестиционный консультант</v>
+        <v>Актуарий | Actuary</v>
       </c>
       <c r="I107" t="str">
-        <v>инвестиции | инвестиционный | investment | инвестиционное консультирование | развитие инвестиционных продуктов | инвестиционный аналитик</v>
+        <v>актуарий | actuary | актуарии | актуарные расчеты</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Trader</v>
+        <v>Investment</v>
       </c>
       <c r="B108" t="str">
         <v>nonit</v>
       </c>
       <c r="C108" t="str">
-        <v/>
+        <v>exec</v>
       </c>
       <c r="D108" t="str">
         <v/>
@@ -3530,21 +3530,21 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>трейдер</v>
+        <v>инвестиционный менеджер</v>
       </c>
       <c r="G108" t="str">
         <v/>
       </c>
       <c r="H108" t="str">
-        <v>Трейдер | Trader | Дилер</v>
+        <v>Investment Manager | Инвестиционный аналитик | инвестиционный консультант</v>
       </c>
       <c r="I108" t="str">
-        <v>трейдер | trader | трейдинг | дилер | трейдеры инвестиций</v>
+        <v>инвестиции | инвестиционный | investment | инвестиционное консультирование | развитие инвестиционных продуктов | инвестиционный аналитик</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Risk</v>
+        <v>Trader</v>
       </c>
       <c r="B109" t="str">
         <v>nonit</v>
@@ -3559,21 +3559,21 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>риск-менеджер</v>
+        <v>трейдер</v>
       </c>
       <c r="G109" t="str">
         <v/>
       </c>
       <c r="H109" t="str">
-        <v>Риск-менеджер | Risk Manager | риск-аналитик</v>
+        <v>Трейдер | Trader | Дилер</v>
       </c>
       <c r="I109" t="str">
-        <v>риск менеджер | risk manager | риск менеджмент | банковский риск | кредитный риск | управление рисками</v>
+        <v>трейдер | trader | трейдинг | дилер | трейдеры инвестиций</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Compliance</v>
+        <v>Risk</v>
       </c>
       <c r="B110" t="str">
         <v>nonit</v>
@@ -3588,21 +3588,21 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>комплаенс-менеджер</v>
+        <v>риск-менеджер</v>
       </c>
       <c r="G110" t="str">
         <v/>
       </c>
       <c r="H110" t="str">
-        <v>Compliance Manager | Комплаенс | специалист по комплаенс</v>
+        <v>Риск-менеджер | Risk Manager | риск-аналитик</v>
       </c>
       <c r="I110" t="str">
-        <v>compliance | комплаенс | антикоррупционный | этический комплаенс | управление compliance | lmc | нормативное сопровождение | регуляторная отчетность | контроль режима санкций | внутренний контроль | свк | финансовый мониторинг | анализ сомнительных операций | kyc | aml</v>
+        <v>риск менеджер | risk manager | риск менеджмент | банковский риск | кредитный риск | управление рисками</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>BankOps</v>
+        <v>Compliance</v>
       </c>
       <c r="B111" t="str">
         <v>nonit</v>
@@ -3617,21 +3617,21 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>специалист банковских операций</v>
+        <v>комплаенс-менеджер</v>
       </c>
       <c r="G111" t="str">
         <v/>
       </c>
       <c r="H111" t="str">
-        <v>Специалист банковских операций | Bank Operations | операционист</v>
+        <v>Compliance Manager | Комплаенс | специалист по комплаенс</v>
       </c>
       <c r="I111" t="str">
-        <v>банковские операции | платежные транзакции | расчетно кассовое | операционист | back office | бэк офис | депозитарий | кастодиальный</v>
+        <v>compliance | комплаенс | антикоррупционный | этический комплаенс | управление compliance | lmc | нормативное сопровождение | регуляторная отчетность | контроль режима санкций | внутренний контроль | свк | финансовый мониторинг | анализ сомнительных операций | kyc | aml</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Payments</v>
+        <v>BankOps</v>
       </c>
       <c r="B112" t="str">
         <v>nonit</v>
@@ -3646,21 +3646,21 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>менеджер платёжных решений</v>
+        <v>специалист банковских операций</v>
       </c>
       <c r="G112" t="str">
         <v/>
       </c>
       <c r="H112" t="str">
-        <v>Payments Manager | развитие платёжных решений | продукт-менеджер платежей</v>
+        <v>Специалист банковских операций | Bank Operations | операционист</v>
       </c>
       <c r="I112" t="str">
-        <v>платежные решения | платежные системы | payments | эквайринг | развитие платежных решений</v>
+        <v>банковские операции | платежные транзакции | расчетно кассовое | операционист | back office | бэк офис | депозитарий | кастодиальный</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Dispute</v>
+        <v>Payments</v>
       </c>
       <c r="B113" t="str">
         <v>nonit</v>
@@ -3675,27 +3675,27 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>диспут-менеджер</v>
+        <v>менеджер платёжных решений</v>
       </c>
       <c r="G113" t="str">
         <v/>
       </c>
       <c r="H113" t="str">
-        <v>Dispute Manager | Диспут-менеджер | специалист по претензиям</v>
+        <v>Payments Manager | развитие платёжных решений | продукт-менеджер платежей</v>
       </c>
       <c r="I113" t="str">
-        <v>диспут менеджер | работа с претензиями | чарджбэк | dispute | претензионная работа</v>
+        <v>платежные решения | платежные системы | payments | эквайринг | развитие платежных решений</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>GR</v>
+        <v>Dispute</v>
       </c>
       <c r="B114" t="str">
         <v>nonit</v>
       </c>
       <c r="C114" t="str">
-        <v>exec</v>
+        <v/>
       </c>
       <c r="D114" t="str">
         <v/>
@@ -3704,27 +3704,27 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>gr-менеджер</v>
+        <v>диспут-менеджер</v>
       </c>
       <c r="G114" t="str">
         <v/>
       </c>
       <c r="H114" t="str">
-        <v>GR Manager | Government Relations | менеджер по взаимодействию с органами власти</v>
+        <v>Dispute Manager | Диспут-менеджер | специалист по претензиям</v>
       </c>
       <c r="I114" t="str">
-        <v xml:space="preserve"> gr  | government relations | взаимодействие с органами власти | связи с государством | gr менеджер</v>
+        <v>диспут менеджер | работа с претензиями | чарджбэк | dispute | претензионная работа</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Recruiter</v>
+        <v>GR</v>
       </c>
       <c r="B115" t="str">
         <v>nonit</v>
       </c>
       <c r="C115" t="str">
-        <v/>
+        <v>exec</v>
       </c>
       <c r="D115" t="str">
         <v/>
@@ -3733,21 +3733,21 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>рекрутер</v>
+        <v>gr-менеджер</v>
       </c>
       <c r="G115" t="str">
         <v/>
       </c>
       <c r="H115" t="str">
-        <v>Рекрутер | IT-рекрутер | Talent Acquisition | Sourcer</v>
+        <v>GR Manager | Government Relations | менеджер по взаимодействию с органами власти</v>
       </c>
       <c r="I115" t="str">
-        <v>рекрутер | recruiter | it рекрутер | talent acquisition | сорсер | sourcer | сорсинг | подбор персонала | рекрутинг | рекрутмент | recruitment</v>
+        <v xml:space="preserve"> gr  | government relations | взаимодействие с органами власти | связи с государством | gr менеджер</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>HRManager</v>
+        <v>Recruiter</v>
       </c>
       <c r="B116" t="str">
         <v>nonit</v>
@@ -3762,21 +3762,21 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>hr-менеджер</v>
+        <v>рекрутер</v>
       </c>
       <c r="G116" t="str">
         <v/>
       </c>
       <c r="H116" t="str">
-        <v>HR-менеджер | HR Generalist | менеджер по персоналу | General HR</v>
+        <v>Рекрутер | IT-рекрутер | Talent Acquisition | Sourcer</v>
       </c>
       <c r="I116" t="str">
-        <v>hr менеджер | эйчар | менеджер по персоналу |  hr  | human resources | general hr</v>
+        <v>рекрутер | recruiter | it рекрутер | talent acquisition | сорсер | sourcer | сорсинг | подбор персонала | рекрутинг | рекрутмент | recruitment</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>HRBP</v>
+        <v>HRManager</v>
       </c>
       <c r="B117" t="str">
         <v>nonit</v>
@@ -3791,21 +3791,21 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>hr бизнес-партнёр</v>
+        <v>hr-менеджер</v>
       </c>
       <c r="G117" t="str">
         <v/>
       </c>
       <c r="H117" t="str">
-        <v>HR Business Partner | HRBP</v>
+        <v>HR-менеджер | HR Generalist | менеджер по персоналу | General HR</v>
       </c>
       <c r="I117" t="str">
-        <v>hrbp | hr бизнес партнер | hr business partner</v>
+        <v>hr менеджер | эйчар | менеджер по персоналу |  hr  | human resources | general hr</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>CnB</v>
+        <v>HRBP</v>
       </c>
       <c r="B118" t="str">
         <v>nonit</v>
@@ -3820,21 +3820,21 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>специалист по компенсациям и льготам</v>
+        <v>hr бизнес-партнёр</v>
       </c>
       <c r="G118" t="str">
         <v/>
       </c>
       <c r="H118" t="str">
-        <v>C&amp;B Specialist | Compensation &amp; Benefits | специалист по C&amp;B</v>
+        <v>HR Business Partner | HRBP</v>
       </c>
       <c r="I118" t="str">
-        <v>c&amp;b | компенсации и льготы | compensation | benefits | партнер по компенсациям | sti compensations</v>
+        <v>hrbp | hr бизнес партнер | hr business partner</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>LnD</v>
+        <v>CnB</v>
       </c>
       <c r="B119" t="str">
         <v>nonit</v>
@@ -3849,21 +3849,21 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>специалист по обучению и развитию</v>
+        <v>специалист по компенсациям и льготам</v>
       </c>
       <c r="G119" t="str">
         <v/>
       </c>
       <c r="H119" t="str">
-        <v>L&amp;D Specialist | Learning &amp; Development | тренинг-менеджер</v>
+        <v>C&amp;B Specialist | Compensation &amp; Benefits | специалист по C&amp;B</v>
       </c>
       <c r="I119" t="str">
-        <v>обучение и развитие | l&amp;d | learning and development | тренинг менеджер | адаптация | автоматизация процессов обучения | t&amp;d | l&amp;d партнер</v>
+        <v>c&amp;b | компенсации и льготы | compensation | benefits | партнер по компенсациям | sti compensations</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>OrgDev</v>
+        <v>LnD</v>
       </c>
       <c r="B120" t="str">
         <v>nonit</v>
@@ -3878,21 +3878,21 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>специалист по орг. развитию</v>
+        <v>специалист по обучению и развитию</v>
       </c>
       <c r="G120" t="str">
         <v/>
       </c>
       <c r="H120" t="str">
-        <v>Organizational Development | орг. развитие</v>
+        <v>L&amp;D Specialist | Learning &amp; Development | тренинг-менеджер</v>
       </c>
       <c r="I120" t="str">
-        <v>организационное развитие | орг развитие | орг. развитие | org development | развитие организации</v>
+        <v>обучение и развитие | l&amp;d | learning and development | тренинг менеджер | адаптация | автоматизация процессов обучения | t&amp;d | l&amp;d партнер</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>HRAdmin</v>
+        <v>OrgDev</v>
       </c>
       <c r="B121" t="str">
         <v>nonit</v>
@@ -3907,21 +3907,21 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>специалист по кадрам</v>
+        <v>специалист по орг. развитию</v>
       </c>
       <c r="G121" t="str">
         <v/>
       </c>
       <c r="H121" t="str">
-        <v>HR Administrator | Кадровое администрирование | специалист по кадровому делопроизводству</v>
+        <v>Organizational Development | орг. развитие</v>
       </c>
       <c r="I121" t="str">
-        <v>кадровое администрирование | кадры | кадровое делопроизводство | кадровик | hr администратор | управление кадровым администрированием</v>
+        <v>организационное развитие | орг развитие | орг. развитие | org development | развитие организации</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>EmployerBrand</v>
+        <v>HRAdmin</v>
       </c>
       <c r="B122" t="str">
         <v>nonit</v>
@@ -3936,21 +3936,21 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>менеджер бренда работодателя</v>
+        <v>специалист по кадрам</v>
       </c>
       <c r="G122" t="str">
         <v/>
       </c>
       <c r="H122" t="str">
-        <v>Employer Brand Manager | HR-маркетолог | менеджер бренда работодателя</v>
+        <v>HR Administrator | Кадровое администрирование | специалист по кадровому делопроизводству</v>
       </c>
       <c r="I122" t="str">
-        <v>бренд работодателя | employer brand | hr бренд | hr маркетинг | hr бренд менеджер</v>
+        <v>кадровое администрирование | кадры | кадровое делопроизводство | кадровик | hr администратор | управление кадровым администрированием</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>InternalComms</v>
+        <v>EmployerBrand</v>
       </c>
       <c r="B123" t="str">
         <v>nonit</v>
@@ -3965,21 +3965,21 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>специалист по внутренним коммуникациям</v>
+        <v>менеджер бренда работодателя</v>
       </c>
       <c r="G123" t="str">
         <v/>
       </c>
       <c r="H123" t="str">
-        <v>Internal Communications | специалист по внутренним коммуникациям</v>
+        <v>Employer Brand Manager | HR-маркетолог | менеджер бренда работодателя</v>
       </c>
       <c r="I123" t="str">
-        <v>внутренние коммуникации | внут коммуникации | внут. коммуникации | internal communications | внутриком | внутренний пиар</v>
+        <v>бренд работодателя | employer brand | hr бренд | hr маркетинг | hr бренд менеджер</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Lawyer</v>
+        <v>InternalComms</v>
       </c>
       <c r="B124" t="str">
         <v>nonit</v>
@@ -3994,21 +3994,21 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>юрист</v>
+        <v>специалист по внутренним коммуникациям</v>
       </c>
       <c r="G124" t="str">
         <v/>
       </c>
       <c r="H124" t="str">
-        <v>Юрист | Юрисконсульт | Legal Counsel | Корпоративный юрист</v>
+        <v>Internal Communications | специалист по внутренним коммуникациям</v>
       </c>
       <c r="I124" t="str">
-        <v>юрист | юрисконсульт | legal counsel | lawyer | адвокат | корпоративный юрист | правовое сопровождение | правовая поддержка | юриспруденция</v>
+        <v>внутренние коммуникации | внут коммуникации | внут. коммуникации | internal communications | внутриком | внутренний пиар</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Procurement</v>
+        <v>Lawyer</v>
       </c>
       <c r="B125" t="str">
         <v>nonit</v>
@@ -4023,21 +4023,21 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>специалист по закупкам</v>
+        <v>юрист</v>
       </c>
       <c r="G125" t="str">
         <v/>
       </c>
       <c r="H125" t="str">
-        <v>Специалист по закупкам | Procurement Manager | Категорийный менеджер</v>
+        <v>Юрист | Юрисконсульт | Legal Counsel | Корпоративный юрист</v>
       </c>
       <c r="I125" t="str">
-        <v>закупки | специалист по закупкам | procurement | снабжение | менеджер по закупкам | категорийный менеджер</v>
+        <v>юрист | юрисконсульт | legal counsel | lawyer | адвокат | корпоративный юрист | правовое сопровождение | правовая поддержка | юриспруденция</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Logistics</v>
+        <v>Procurement</v>
       </c>
       <c r="B126" t="str">
         <v>nonit</v>
@@ -4046,27 +4046,27 @@
         <v/>
       </c>
       <c r="D126" t="str">
-        <v>logist</v>
+        <v/>
       </c>
       <c r="E126" t="str">
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>логист</v>
+        <v>специалист по закупкам</v>
       </c>
       <c r="G126" t="str">
         <v/>
       </c>
       <c r="H126" t="str">
-        <v>Логист | Менеджер по логистике | Специалист по ВЭД | Supply Chain Manager</v>
+        <v>Специалист по закупкам | Procurement Manager | Категорийный менеджер</v>
       </c>
       <c r="I126" t="str">
-        <v>логист | логистика | менеджер по логистике | вэд | специалист по вэд | supply chain | цепочки поставок</v>
+        <v>закупки | специалист по закупкам | procurement | снабжение | менеджер по закупкам | категорийный менеджер</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Warehouse</v>
+        <v>Logistics</v>
       </c>
       <c r="B127" t="str">
         <v>nonit</v>
@@ -4081,21 +4081,21 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>заведующий складом</v>
+        <v>логист</v>
       </c>
       <c r="G127" t="str">
         <v/>
       </c>
       <c r="H127" t="str">
-        <v>Начальник склада | Заведующий складом | Warehouse Manager</v>
+        <v>Логист | Менеджер по логистике | Специалист по ВЭД | Supply Chain Manager</v>
       </c>
       <c r="I127" t="str">
-        <v>начальник склада | заведующий складом | warehouse | складская логистика | кладовщик</v>
+        <v>логист | логистика | менеджер по логистике | вэд | специалист по вэд | supply chain | цепочки поставок</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Support</v>
+        <v>Warehouse</v>
       </c>
       <c r="B128" t="str">
         <v>nonit</v>
@@ -4104,27 +4104,27 @@
         <v/>
       </c>
       <c r="D128" t="str">
-        <v/>
+        <v>logist</v>
       </c>
       <c r="E128" t="str">
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>специалист поддержки</v>
+        <v>заведующий складом</v>
       </c>
       <c r="G128" t="str">
         <v/>
       </c>
       <c r="H128" t="str">
-        <v>Специалист поддержки | Customer Support | Service Desk</v>
+        <v>Начальник склада | Заведующий складом | Warehouse Manager</v>
       </c>
       <c r="I128" t="str">
-        <v>специалист поддержки | customer support | support | техподдержка | служба поддержки | helpdesk | service desk | саппорт | поддержк</v>
+        <v>начальник склада | заведующий складом | warehouse | складская логистика | кладовщик</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>OfficeManager</v>
+        <v>Support</v>
       </c>
       <c r="B129" t="str">
         <v>nonit</v>
@@ -4139,50 +4139,79 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>офис-менеджер</v>
+        <v>специалист поддержки</v>
       </c>
       <c r="G129" t="str">
         <v/>
       </c>
       <c r="H129" t="str">
-        <v>Офис-менеджер | Office Manager | Административный помощник</v>
+        <v>Специалист поддержки | Customer Support | Service Desk</v>
       </c>
       <c r="I129" t="str">
-        <v>офис менеджер | office manager | администратор офиса | ассистент руководителя | секретарь</v>
+        <v>специалист поддержки | customer support | support | техподдержка | служба поддержки | helpdesk | service desk | саппорт | поддержк</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
+        <v>OfficeManager</v>
+      </c>
+      <c r="B130" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C130" t="str">
+        <v/>
+      </c>
+      <c r="D130" t="str">
+        <v/>
+      </c>
+      <c r="E130" t="str">
+        <v/>
+      </c>
+      <c r="F130" t="str">
+        <v>офис-менеджер</v>
+      </c>
+      <c r="G130" t="str">
+        <v/>
+      </c>
+      <c r="H130" t="str">
+        <v>Офис-менеджер | Office Manager | Административный помощник</v>
+      </c>
+      <c r="I130" t="str">
+        <v>офис менеджер | office manager | администратор офиса | ассистент руководителя | секретарь</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
         <v>GraphicDesigner</v>
       </c>
-      <c r="B130" t="str">
-        <v>nonit</v>
-      </c>
-      <c r="C130" t="str">
-        <v/>
-      </c>
-      <c r="D130" t="str">
+      <c r="B131" t="str">
+        <v>nonit</v>
+      </c>
+      <c r="C131" t="str">
+        <v/>
+      </c>
+      <c r="D131" t="str">
         <v>behance | dribbble</v>
       </c>
-      <c r="E130" t="str">
-        <v/>
-      </c>
-      <c r="F130" t="str">
+      <c r="E131" t="str">
+        <v/>
+      </c>
+      <c r="F131" t="str">
         <v>графический дизайнер</v>
       </c>
-      <c r="G130" t="str">
-        <v/>
-      </c>
-      <c r="H130" t="str">
+      <c r="G131" t="str">
+        <v/>
+      </c>
+      <c r="H131" t="str">
         <v>Графический дизайнер | Graphic Designer | Motion Designer | бренд-дизайнер</v>
       </c>
-      <c r="I130" t="str">
+      <c r="I131" t="str">
         <v>графический дизайнер | graphic designer | графический дизайн | бренд дизайн | брендинг | моушн дизайнер | motion designer | веб дизайнер | дизайнер</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I130"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I131"/>
   </ignoredErrors>
 </worksheet>
 </file>